--- a/PO_matcall.XLSX
+++ b/PO_matcall.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3182" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3422" uniqueCount="281">
   <si>
     <t>0102000001</t>
   </si>
@@ -400,6 +400,33 @@
     <t>0105090126</t>
   </si>
   <si>
+    <t>0102004048</t>
+  </si>
+  <si>
+    <t>0105103667</t>
+  </si>
+  <si>
+    <t>0010028488</t>
+  </si>
+  <si>
+    <t>อินกริดิออน สวีทเท็นเนอร์ แอนด์ สตาร์ช(ประเทศไทย)</t>
+  </si>
+  <si>
+    <t>000000000120001474</t>
+  </si>
+  <si>
+    <t>Bioligo (IMO)</t>
+  </si>
+  <si>
+    <t>12-200</t>
+  </si>
+  <si>
+    <t>0102004049</t>
+  </si>
+  <si>
+    <t>0105103666</t>
+  </si>
+  <si>
     <t>0102004610</t>
   </si>
   <si>
@@ -607,6 +634,12 @@
     <t>0105102679</t>
   </si>
   <si>
+    <t>0102007548</t>
+  </si>
+  <si>
+    <t>0105103664</t>
+  </si>
+  <si>
     <t>0102007613</t>
   </si>
   <si>
@@ -617,6 +650,33 @@
   </si>
   <si>
     <t>0105104218</t>
+  </si>
+  <si>
+    <t>0102007637</t>
+  </si>
+  <si>
+    <t>0105107630</t>
+  </si>
+  <si>
+    <t>0105107631</t>
+  </si>
+  <si>
+    <t>0105107633</t>
+  </si>
+  <si>
+    <t>0105107634</t>
+  </si>
+  <si>
+    <t>0102007639</t>
+  </si>
+  <si>
+    <t>0105107635</t>
+  </si>
+  <si>
+    <t>0102007641</t>
+  </si>
+  <si>
+    <t>0105107637</t>
   </si>
   <si>
     <t>0102007666</t>
@@ -906,7 +966,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL132"/>
+  <dimension ref="A1:AL142"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="18" customWidth="1"/>
@@ -921,7 +981,7 @@
     <col min="10" max="10" bestFit="1" width="7" customWidth="1"/>
     <col min="11" max="11" bestFit="1" width="19" customWidth="1"/>
     <col min="12" max="12" bestFit="1" width="12" customWidth="1"/>
-    <col min="13" max="13" bestFit="1" width="29" customWidth="1"/>
+    <col min="13" max="13" bestFit="1" width="51" customWidth="1"/>
     <col min="14" max="14" bestFit="1" width="9" customWidth="1"/>
     <col min="15" max="15" bestFit="1" width="13" customWidth="1"/>
     <col min="16" max="16" bestFit="1" width="13" customWidth="1"/>
@@ -951,118 +1011,118 @@
   <sheetData>
     <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="AH1" s="6" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="AI1" s="6" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="AL1" s="6" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:38">
@@ -7224,19 +7284,19 @@
         <v>2</v>
       </c>
       <c r="D55" s="2">
-        <v>46135</v>
+        <v>46122</v>
       </c>
       <c r="E55" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="F55" t="s">
         <v>1</v>
       </c>
       <c r="G55" s="2">
-        <v>45997</v>
+        <v>46122</v>
       </c>
       <c r="H55" s="2">
-        <v>46141</v>
+        <v>46122</v>
       </c>
       <c r="I55" t="s">
         <v>4</v>
@@ -7248,10 +7308,10 @@
         <v>40</v>
       </c>
       <c r="L55" t="s">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="M55" t="s">
-        <v>62</v>
+        <v>132</v>
       </c>
       <c r="N55" t="s">
         <v>9</v>
@@ -7263,25 +7323,25 @@
         <v>9</v>
       </c>
       <c r="Q55" t="s">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="R55" t="s">
-        <v>64</v>
+        <v>134</v>
       </c>
       <c r="S55" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="T55" t="s">
         <v>13</v>
       </c>
       <c r="U55" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="V55" s="3">
-        <v>30000.000</v>
+        <v>35000.000</v>
       </c>
       <c r="W55" s="3">
-        <v>30000.000</v>
+        <v>28000.000</v>
       </c>
       <c r="X55" s="3">
         <v>0.000</v>
@@ -7290,19 +7350,19 @@
         <v>15</v>
       </c>
       <c r="Z55" s="2">
-        <v>46137</v>
+        <v>46121</v>
       </c>
       <c r="AA55" s="2">
-        <v>46136</v>
+        <v>46211</v>
       </c>
       <c r="AB55" s="2">
-        <v>46137</v>
+        <v>46123</v>
       </c>
       <c r="AC55" s="4">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AD55" s="5">
-        <v>13.50</v>
+        <v>47.00</v>
       </c>
       <c r="AE55" t="s">
         <v>16</v>
@@ -7311,10 +7371,10 @@
         <v>1</v>
       </c>
       <c r="AG55" s="5">
-        <v>405000.00</v>
+        <v>1645000.00</v>
       </c>
       <c r="AH55" s="5">
-        <v>405000.00</v>
+        <v>1316000.00</v>
       </c>
       <c r="AI55" t="s">
         <v>17</v>
@@ -7331,28 +7391,28 @@
     </row>
     <row r="56" spans="1:38">
       <c r="A56" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B56" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C56" t="s">
         <v>2</v>
       </c>
       <c r="D56" s="2">
-        <v>46135</v>
+        <v>46122</v>
       </c>
       <c r="E56" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F56" t="s">
         <v>1</v>
       </c>
       <c r="G56" s="2">
-        <v>45997</v>
+        <v>46122</v>
       </c>
       <c r="H56" s="2">
-        <v>46135</v>
+        <v>46122</v>
       </c>
       <c r="I56" t="s">
         <v>4</v>
@@ -7364,10 +7424,10 @@
         <v>40</v>
       </c>
       <c r="L56" t="s">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="M56" t="s">
-        <v>62</v>
+        <v>132</v>
       </c>
       <c r="N56" t="s">
         <v>9</v>
@@ -7379,25 +7439,25 @@
         <v>9</v>
       </c>
       <c r="Q56" t="s">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="R56" t="s">
-        <v>64</v>
+        <v>134</v>
       </c>
       <c r="S56" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="T56" t="s">
         <v>13</v>
       </c>
       <c r="U56" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="V56" s="3">
-        <v>80000.000</v>
+        <v>19600.000</v>
       </c>
       <c r="W56" s="3">
-        <v>80000.000</v>
+        <v>16800.000</v>
       </c>
       <c r="X56" s="3">
         <v>0.000</v>
@@ -7406,19 +7466,19 @@
         <v>15</v>
       </c>
       <c r="Z56" s="2">
-        <v>46139</v>
+        <v>46177</v>
       </c>
       <c r="AA56" s="2">
-        <v>46136</v>
+        <v>46211</v>
       </c>
       <c r="AB56" s="2">
-        <v>46137</v>
+        <v>46143</v>
       </c>
       <c r="AC56" s="4">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="AD56" s="5">
-        <v>13.50</v>
+        <v>47.00</v>
       </c>
       <c r="AE56" t="s">
         <v>16</v>
@@ -7427,10 +7487,10 @@
         <v>1</v>
       </c>
       <c r="AG56" s="5">
-        <v>1080000.00</v>
+        <v>921200.00</v>
       </c>
       <c r="AH56" s="5">
-        <v>1080000.00</v>
+        <v>789600.00</v>
       </c>
       <c r="AI56" t="s">
         <v>17</v>
@@ -7447,7 +7507,7 @@
     </row>
     <row r="57" spans="1:38">
       <c r="A57" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B57" t="s">
         <v>1</v>
@@ -7459,16 +7519,16 @@
         <v>46135</v>
       </c>
       <c r="E57" t="s">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="F57" t="s">
         <v>1</v>
       </c>
       <c r="G57" s="2">
-        <v>45814</v>
+        <v>45997</v>
       </c>
       <c r="H57" s="2">
-        <v>46135</v>
+        <v>46141</v>
       </c>
       <c r="I57" t="s">
         <v>4</v>
@@ -7480,10 +7540,10 @@
         <v>40</v>
       </c>
       <c r="L57" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="M57" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="N57" t="s">
         <v>9</v>
@@ -7495,10 +7555,10 @@
         <v>9</v>
       </c>
       <c r="Q57" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="R57" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="S57" t="s">
         <v>12</v>
@@ -7510,10 +7570,10 @@
         <v>45</v>
       </c>
       <c r="V57" s="3">
-        <v>280500.000</v>
+        <v>30000.000</v>
       </c>
       <c r="W57" s="3">
-        <v>280500.000</v>
+        <v>30000.000</v>
       </c>
       <c r="X57" s="3">
         <v>0.000</v>
@@ -7522,19 +7582,19 @@
         <v>15</v>
       </c>
       <c r="Z57" s="2">
-        <v>46144</v>
+        <v>46137</v>
       </c>
       <c r="AA57" s="2">
-        <v>46142</v>
+        <v>46136</v>
       </c>
       <c r="AB57" s="2">
-        <v>46143</v>
+        <v>46137</v>
       </c>
       <c r="AC57" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD57" s="5">
-        <v>15.34</v>
+        <v>13.50</v>
       </c>
       <c r="AE57" t="s">
         <v>16</v>
@@ -7543,10 +7603,10 @@
         <v>1</v>
       </c>
       <c r="AG57" s="5">
-        <v>4302870.00</v>
+        <v>405000.00</v>
       </c>
       <c r="AH57" s="5">
-        <v>4302870.00</v>
+        <v>405000.00</v>
       </c>
       <c r="AI57" t="s">
         <v>17</v>
@@ -7563,7 +7623,7 @@
     </row>
     <row r="58" spans="1:38">
       <c r="A58" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B58" t="s">
         <v>19</v>
@@ -7575,13 +7635,13 @@
         <v>46135</v>
       </c>
       <c r="E58" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="F58" t="s">
         <v>1</v>
       </c>
       <c r="G58" s="2">
-        <v>45814</v>
+        <v>45997</v>
       </c>
       <c r="H58" s="2">
         <v>46135</v>
@@ -7596,10 +7656,10 @@
         <v>40</v>
       </c>
       <c r="L58" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="M58" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="N58" t="s">
         <v>9</v>
@@ -7611,10 +7671,10 @@
         <v>9</v>
       </c>
       <c r="Q58" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="R58" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="S58" t="s">
         <v>12</v>
@@ -7626,10 +7686,10 @@
         <v>45</v>
       </c>
       <c r="V58" s="3">
-        <v>280500.000</v>
+        <v>80000.000</v>
       </c>
       <c r="W58" s="3">
-        <v>280500.000</v>
+        <v>80000.000</v>
       </c>
       <c r="X58" s="3">
         <v>0.000</v>
@@ -7638,19 +7698,19 @@
         <v>15</v>
       </c>
       <c r="Z58" s="2">
-        <v>46147</v>
+        <v>46139</v>
       </c>
       <c r="AA58" s="2">
-        <v>46142</v>
+        <v>46136</v>
       </c>
       <c r="AB58" s="2">
-        <v>46143</v>
+        <v>46137</v>
       </c>
       <c r="AC58" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AD58" s="5">
-        <v>15.34</v>
+        <v>13.50</v>
       </c>
       <c r="AE58" t="s">
         <v>16</v>
@@ -7659,10 +7719,10 @@
         <v>1</v>
       </c>
       <c r="AG58" s="5">
-        <v>4302870.00</v>
+        <v>1080000.00</v>
       </c>
       <c r="AH58" s="5">
-        <v>4302870.00</v>
+        <v>1080000.00</v>
       </c>
       <c r="AI58" t="s">
         <v>17</v>
@@ -7679,10 +7739,10 @@
     </row>
     <row r="59" spans="1:38">
       <c r="A59" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B59" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C59" t="s">
         <v>2</v>
@@ -7691,7 +7751,7 @@
         <v>46135</v>
       </c>
       <c r="E59" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="F59" t="s">
         <v>1</v>
@@ -7745,16 +7805,16 @@
         <v>280500.000</v>
       </c>
       <c r="W59" s="3">
-        <v>98460.000</v>
+        <v>280500.000</v>
       </c>
       <c r="X59" s="3">
-        <v>182040.000</v>
+        <v>0.000</v>
       </c>
       <c r="Y59" t="s">
         <v>15</v>
       </c>
       <c r="Z59" s="2">
-        <v>46168</v>
+        <v>46144</v>
       </c>
       <c r="AA59" s="2">
         <v>46142</v>
@@ -7763,7 +7823,7 @@
         <v>46143</v>
       </c>
       <c r="AC59" s="4">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AD59" s="5">
         <v>15.34</v>
@@ -7778,10 +7838,10 @@
         <v>4302870.00</v>
       </c>
       <c r="AH59" s="5">
-        <v>1510376.40</v>
+        <v>4302870.00</v>
       </c>
       <c r="AI59" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AJ59" t="s">
         <v>9</v>
@@ -7795,10 +7855,10 @@
     </row>
     <row r="60" spans="1:38">
       <c r="A60" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B60" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="C60" t="s">
         <v>2</v>
@@ -7807,13 +7867,13 @@
         <v>46135</v>
       </c>
       <c r="E60" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F60" t="s">
         <v>1</v>
       </c>
       <c r="G60" s="2">
-        <v>45995</v>
+        <v>45814</v>
       </c>
       <c r="H60" s="2">
         <v>46135</v>
@@ -7858,10 +7918,10 @@
         <v>45</v>
       </c>
       <c r="V60" s="3">
-        <v>150000.000</v>
+        <v>280500.000</v>
       </c>
       <c r="W60" s="3">
-        <v>150000.000</v>
+        <v>280500.000</v>
       </c>
       <c r="X60" s="3">
         <v>0.000</v>
@@ -7870,7 +7930,7 @@
         <v>15</v>
       </c>
       <c r="Z60" s="2">
-        <v>46161</v>
+        <v>46147</v>
       </c>
       <c r="AA60" s="2">
         <v>46142</v>
@@ -7879,7 +7939,7 @@
         <v>46143</v>
       </c>
       <c r="AC60" s="4">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="AD60" s="5">
         <v>15.34</v>
@@ -7891,10 +7951,10 @@
         <v>1</v>
       </c>
       <c r="AG60" s="5">
-        <v>2301000.00</v>
+        <v>4302870.00</v>
       </c>
       <c r="AH60" s="5">
-        <v>2301000.00</v>
+        <v>4302870.00</v>
       </c>
       <c r="AI60" t="s">
         <v>17</v>
@@ -7911,10 +7971,10 @@
     </row>
     <row r="61" spans="1:38">
       <c r="A61" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B61" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C61" t="s">
         <v>2</v>
@@ -7923,13 +7983,13 @@
         <v>46135</v>
       </c>
       <c r="E61" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F61" t="s">
         <v>1</v>
       </c>
       <c r="G61" s="2">
-        <v>45997</v>
+        <v>45814</v>
       </c>
       <c r="H61" s="2">
         <v>46135</v>
@@ -7944,10 +8004,10 @@
         <v>40</v>
       </c>
       <c r="L61" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="M61" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="N61" t="s">
         <v>9</v>
@@ -7965,7 +8025,7 @@
         <v>44</v>
       </c>
       <c r="S61" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="T61" t="s">
         <v>13</v>
@@ -7974,19 +8034,19 @@
         <v>45</v>
       </c>
       <c r="V61" s="3">
-        <v>240000.000</v>
+        <v>280500.000</v>
       </c>
       <c r="W61" s="3">
-        <v>239840.000</v>
+        <v>98460.000</v>
       </c>
       <c r="X61" s="3">
-        <v>160.000</v>
+        <v>182040.000</v>
       </c>
       <c r="Y61" t="s">
         <v>15</v>
       </c>
       <c r="Z61" s="2">
-        <v>46144</v>
+        <v>46168</v>
       </c>
       <c r="AA61" s="2">
         <v>46142</v>
@@ -7995,10 +8055,10 @@
         <v>46143</v>
       </c>
       <c r="AC61" s="4">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AD61" s="5">
-        <v>15.42</v>
+        <v>15.34</v>
       </c>
       <c r="AE61" t="s">
         <v>16</v>
@@ -8007,10 +8067,10 @@
         <v>1</v>
       </c>
       <c r="AG61" s="5">
-        <v>3700800.00</v>
+        <v>4302870.00</v>
       </c>
       <c r="AH61" s="5">
-        <v>3698332.80</v>
+        <v>1510376.40</v>
       </c>
       <c r="AI61" t="s">
         <v>9</v>
@@ -8027,10 +8087,10 @@
     </row>
     <row r="62" spans="1:38">
       <c r="A62" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B62" t="s">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="C62" t="s">
         <v>2</v>
@@ -8039,13 +8099,13 @@
         <v>46135</v>
       </c>
       <c r="E62" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="F62" t="s">
         <v>1</v>
       </c>
       <c r="G62" s="2">
-        <v>45997</v>
+        <v>45995</v>
       </c>
       <c r="H62" s="2">
         <v>46135</v>
@@ -8081,7 +8141,7 @@
         <v>44</v>
       </c>
       <c r="S62" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T62" t="s">
         <v>13</v>
@@ -8090,10 +8150,10 @@
         <v>45</v>
       </c>
       <c r="V62" s="3">
-        <v>60000.000</v>
+        <v>150000.000</v>
       </c>
       <c r="W62" s="3">
-        <v>29980.000</v>
+        <v>150000.000</v>
       </c>
       <c r="X62" s="3">
         <v>0.000</v>
@@ -8102,19 +8162,19 @@
         <v>15</v>
       </c>
       <c r="Z62" s="2">
-        <v>46141</v>
+        <v>46161</v>
       </c>
       <c r="AA62" s="2">
-        <v>46154</v>
+        <v>46142</v>
       </c>
       <c r="AB62" s="2">
-        <v>46139</v>
+        <v>46143</v>
       </c>
       <c r="AC62" s="4">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="AD62" s="5">
-        <v>15.32</v>
+        <v>15.34</v>
       </c>
       <c r="AE62" t="s">
         <v>16</v>
@@ -8123,10 +8183,10 @@
         <v>1</v>
       </c>
       <c r="AG62" s="5">
-        <v>919200.00</v>
+        <v>2301000.00</v>
       </c>
       <c r="AH62" s="5">
-        <v>459293.60</v>
+        <v>2301000.00</v>
       </c>
       <c r="AI62" t="s">
         <v>17</v>
@@ -8143,7 +8203,7 @@
     </row>
     <row r="63" spans="1:38">
       <c r="A63" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B63" t="s">
         <v>1</v>
@@ -8155,7 +8215,7 @@
         <v>46135</v>
       </c>
       <c r="E63" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F63" t="s">
         <v>1</v>
@@ -8197,40 +8257,40 @@
         <v>44</v>
       </c>
       <c r="S63" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="T63" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="U63" t="s">
         <v>45</v>
       </c>
       <c r="V63" s="3">
-        <v>31000.000</v>
+        <v>240000.000</v>
       </c>
       <c r="W63" s="3">
-        <v>30980.000</v>
+        <v>239840.000</v>
       </c>
       <c r="X63" s="3">
-        <v>0.000</v>
+        <v>160.000</v>
       </c>
       <c r="Y63" t="s">
         <v>15</v>
       </c>
       <c r="Z63" s="2">
-        <v>46141</v>
+        <v>46144</v>
       </c>
       <c r="AA63" s="2">
-        <v>46154</v>
+        <v>46142</v>
       </c>
       <c r="AB63" s="2">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="AC63" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD63" s="5">
-        <v>15.20</v>
+        <v>15.42</v>
       </c>
       <c r="AE63" t="s">
         <v>16</v>
@@ -8239,13 +8299,13 @@
         <v>1</v>
       </c>
       <c r="AG63" s="5">
-        <v>471200.00</v>
+        <v>3700800.00</v>
       </c>
       <c r="AH63" s="5">
-        <v>470896.00</v>
+        <v>3698332.80</v>
       </c>
       <c r="AI63" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AJ63" t="s">
         <v>9</v>
@@ -8259,7 +8319,7 @@
     </row>
     <row r="64" spans="1:38">
       <c r="A64" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B64" t="s">
         <v>1</v>
@@ -8268,10 +8328,10 @@
         <v>2</v>
       </c>
       <c r="D64" s="2">
-        <v>46136</v>
+        <v>46135</v>
       </c>
       <c r="E64" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="F64" t="s">
         <v>1</v>
@@ -8292,10 +8352,10 @@
         <v>40</v>
       </c>
       <c r="L64" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M64" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="N64" t="s">
         <v>9</v>
@@ -8307,13 +8367,13 @@
         <v>9</v>
       </c>
       <c r="Q64" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="R64" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="S64" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T64" t="s">
         <v>13</v>
@@ -8322,10 +8382,10 @@
         <v>45</v>
       </c>
       <c r="V64" s="3">
-        <v>25000.000</v>
+        <v>60000.000</v>
       </c>
       <c r="W64" s="3">
-        <v>25000.000</v>
+        <v>29980.000</v>
       </c>
       <c r="X64" s="3">
         <v>0.000</v>
@@ -8334,19 +8394,19 @@
         <v>15</v>
       </c>
       <c r="Z64" s="2">
-        <v>46142</v>
+        <v>46141</v>
       </c>
       <c r="AA64" s="2">
-        <v>46140</v>
+        <v>46154</v>
       </c>
       <c r="AB64" s="2">
-        <v>46142</v>
+        <v>46139</v>
       </c>
       <c r="AC64" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD64" s="5">
-        <v>13.50</v>
+        <v>15.32</v>
       </c>
       <c r="AE64" t="s">
         <v>16</v>
@@ -8355,10 +8415,10 @@
         <v>1</v>
       </c>
       <c r="AG64" s="5">
-        <v>337500.00</v>
+        <v>919200.00</v>
       </c>
       <c r="AH64" s="5">
-        <v>337500.00</v>
+        <v>459293.60</v>
       </c>
       <c r="AI64" t="s">
         <v>17</v>
@@ -8375,7 +8435,7 @@
     </row>
     <row r="65" spans="1:38">
       <c r="A65" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B65" t="s">
         <v>1</v>
@@ -8384,10 +8444,10 @@
         <v>2</v>
       </c>
       <c r="D65" s="2">
-        <v>46139</v>
+        <v>46135</v>
       </c>
       <c r="E65" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="F65" t="s">
         <v>1</v>
@@ -8408,10 +8468,10 @@
         <v>40</v>
       </c>
       <c r="L65" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="M65" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="N65" t="s">
         <v>9</v>
@@ -8429,19 +8489,19 @@
         <v>44</v>
       </c>
       <c r="S65" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="T65" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="U65" t="s">
         <v>45</v>
       </c>
       <c r="V65" s="3">
-        <v>100000.000</v>
+        <v>31000.000</v>
       </c>
       <c r="W65" s="3">
-        <v>100000.000</v>
+        <v>30980.000</v>
       </c>
       <c r="X65" s="3">
         <v>0.000</v>
@@ -8450,19 +8510,19 @@
         <v>15</v>
       </c>
       <c r="Z65" s="2">
-        <v>46147</v>
+        <v>46141</v>
       </c>
       <c r="AA65" s="2">
-        <v>46142</v>
+        <v>46154</v>
       </c>
       <c r="AB65" s="2">
-        <v>46143</v>
+        <v>46141</v>
       </c>
       <c r="AC65" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD65" s="5">
-        <v>15.42</v>
+        <v>15.20</v>
       </c>
       <c r="AE65" t="s">
         <v>16</v>
@@ -8471,10 +8531,10 @@
         <v>1</v>
       </c>
       <c r="AG65" s="5">
-        <v>1542000.00</v>
+        <v>471200.00</v>
       </c>
       <c r="AH65" s="5">
-        <v>1542000.00</v>
+        <v>470896.00</v>
       </c>
       <c r="AI65" t="s">
         <v>17</v>
@@ -8491,19 +8551,19 @@
     </row>
     <row r="66" spans="1:38">
       <c r="A66" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B66" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C66" t="s">
         <v>2</v>
       </c>
       <c r="D66" s="2">
-        <v>46139</v>
+        <v>46136</v>
       </c>
       <c r="E66" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F66" t="s">
         <v>1</v>
@@ -8512,7 +8572,7 @@
         <v>45997</v>
       </c>
       <c r="H66" s="2">
-        <v>46139</v>
+        <v>46135</v>
       </c>
       <c r="I66" t="s">
         <v>4</v>
@@ -8524,10 +8584,10 @@
         <v>40</v>
       </c>
       <c r="L66" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="M66" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="N66" t="s">
         <v>9</v>
@@ -8539,13 +8599,13 @@
         <v>9</v>
       </c>
       <c r="Q66" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="R66" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="S66" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T66" t="s">
         <v>13</v>
@@ -8554,10 +8614,10 @@
         <v>45</v>
       </c>
       <c r="V66" s="3">
-        <v>200000.000</v>
+        <v>25000.000</v>
       </c>
       <c r="W66" s="3">
-        <v>169820.000</v>
+        <v>25000.000</v>
       </c>
       <c r="X66" s="3">
         <v>0.000</v>
@@ -8566,19 +8626,19 @@
         <v>15</v>
       </c>
       <c r="Z66" s="2">
-        <v>46154</v>
+        <v>46142</v>
       </c>
       <c r="AA66" s="2">
-        <v>46200</v>
+        <v>46140</v>
       </c>
       <c r="AB66" s="2">
-        <v>46143</v>
+        <v>46142</v>
       </c>
       <c r="AC66" s="4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AD66" s="5">
-        <v>15.42</v>
+        <v>13.50</v>
       </c>
       <c r="AE66" t="s">
         <v>16</v>
@@ -8587,10 +8647,10 @@
         <v>1</v>
       </c>
       <c r="AG66" s="5">
-        <v>3084000.00</v>
+        <v>337500.00</v>
       </c>
       <c r="AH66" s="5">
-        <v>2618624.40</v>
+        <v>337500.00</v>
       </c>
       <c r="AI66" t="s">
         <v>17</v>
@@ -8607,7 +8667,7 @@
     </row>
     <row r="67" spans="1:38">
       <c r="A67" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B67" t="s">
         <v>1</v>
@@ -8619,7 +8679,7 @@
         <v>46139</v>
       </c>
       <c r="E67" t="s">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="F67" t="s">
         <v>1</v>
@@ -8628,7 +8688,7 @@
         <v>45997</v>
       </c>
       <c r="H67" s="2">
-        <v>46072</v>
+        <v>46135</v>
       </c>
       <c r="I67" t="s">
         <v>4</v>
@@ -8661,7 +8721,7 @@
         <v>44</v>
       </c>
       <c r="S67" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="T67" t="s">
         <v>13</v>
@@ -8670,10 +8730,10 @@
         <v>45</v>
       </c>
       <c r="V67" s="3">
-        <v>60000.000</v>
+        <v>100000.000</v>
       </c>
       <c r="W67" s="3">
-        <v>59960.000</v>
+        <v>100000.000</v>
       </c>
       <c r="X67" s="3">
         <v>0.000</v>
@@ -8685,7 +8745,7 @@
         <v>46147</v>
       </c>
       <c r="AA67" s="2">
-        <v>46200</v>
+        <v>46142</v>
       </c>
       <c r="AB67" s="2">
         <v>46143</v>
@@ -8694,7 +8754,7 @@
         <v>4</v>
       </c>
       <c r="AD67" s="5">
-        <v>16.27</v>
+        <v>15.42</v>
       </c>
       <c r="AE67" t="s">
         <v>16</v>
@@ -8703,10 +8763,10 @@
         <v>1</v>
       </c>
       <c r="AG67" s="5">
-        <v>976200.00</v>
+        <v>1542000.00</v>
       </c>
       <c r="AH67" s="5">
-        <v>975549.20</v>
+        <v>1542000.00</v>
       </c>
       <c r="AI67" t="s">
         <v>17</v>
@@ -8723,10 +8783,10 @@
     </row>
     <row r="68" spans="1:38">
       <c r="A68" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B68" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C68" t="s">
         <v>2</v>
@@ -8735,7 +8795,7 @@
         <v>46139</v>
       </c>
       <c r="E68" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="F68" t="s">
         <v>1</v>
@@ -8744,7 +8804,7 @@
         <v>45997</v>
       </c>
       <c r="H68" s="2">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="I68" t="s">
         <v>4</v>
@@ -8756,10 +8816,10 @@
         <v>40</v>
       </c>
       <c r="L68" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="M68" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="N68" t="s">
         <v>9</v>
@@ -8777,19 +8837,19 @@
         <v>44</v>
       </c>
       <c r="S68" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="T68" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="U68" t="s">
         <v>45</v>
       </c>
       <c r="V68" s="3">
-        <v>217000.000</v>
+        <v>200000.000</v>
       </c>
       <c r="W68" s="3">
-        <v>216860.000</v>
+        <v>169820.000</v>
       </c>
       <c r="X68" s="3">
         <v>0.000</v>
@@ -8798,7 +8858,7 @@
         <v>15</v>
       </c>
       <c r="Z68" s="2">
-        <v>46147</v>
+        <v>46154</v>
       </c>
       <c r="AA68" s="2">
         <v>46200</v>
@@ -8807,10 +8867,10 @@
         <v>46143</v>
       </c>
       <c r="AC68" s="4">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AD68" s="5">
-        <v>15.35</v>
+        <v>15.42</v>
       </c>
       <c r="AE68" t="s">
         <v>16</v>
@@ -8819,10 +8879,10 @@
         <v>1</v>
       </c>
       <c r="AG68" s="5">
-        <v>3330950.00</v>
+        <v>3084000.00</v>
       </c>
       <c r="AH68" s="5">
-        <v>3328801.00</v>
+        <v>2618624.40</v>
       </c>
       <c r="AI68" t="s">
         <v>17</v>
@@ -8839,7 +8899,7 @@
     </row>
     <row r="69" spans="1:38">
       <c r="A69" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B69" t="s">
         <v>1</v>
@@ -8848,10 +8908,10 @@
         <v>2</v>
       </c>
       <c r="D69" s="2">
-        <v>46141</v>
+        <v>46139</v>
       </c>
       <c r="E69" t="s">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="F69" t="s">
         <v>1</v>
@@ -8860,7 +8920,7 @@
         <v>45997</v>
       </c>
       <c r="H69" s="2">
-        <v>46141</v>
+        <v>46072</v>
       </c>
       <c r="I69" t="s">
         <v>4</v>
@@ -8872,10 +8932,10 @@
         <v>40</v>
       </c>
       <c r="L69" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="M69" t="s">
-        <v>149</v>
+        <v>51</v>
       </c>
       <c r="N69" t="s">
         <v>9</v>
@@ -8887,13 +8947,13 @@
         <v>9</v>
       </c>
       <c r="Q69" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="R69" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="S69" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="T69" t="s">
         <v>13</v>
@@ -8902,10 +8962,10 @@
         <v>45</v>
       </c>
       <c r="V69" s="3">
-        <v>80000.000</v>
+        <v>60000.000</v>
       </c>
       <c r="W69" s="3">
-        <v>80000.000</v>
+        <v>59960.000</v>
       </c>
       <c r="X69" s="3">
         <v>0.000</v>
@@ -8914,19 +8974,19 @@
         <v>15</v>
       </c>
       <c r="Z69" s="2">
-        <v>46163</v>
+        <v>46147</v>
       </c>
       <c r="AA69" s="2">
-        <v>46149</v>
+        <v>46200</v>
       </c>
       <c r="AB69" s="2">
         <v>46143</v>
       </c>
       <c r="AC69" s="4">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="AD69" s="5">
-        <v>14.50</v>
+        <v>16.27</v>
       </c>
       <c r="AE69" t="s">
         <v>16</v>
@@ -8935,10 +8995,10 @@
         <v>1</v>
       </c>
       <c r="AG69" s="5">
-        <v>1160000.00</v>
+        <v>976200.00</v>
       </c>
       <c r="AH69" s="5">
-        <v>1160000.00</v>
+        <v>975549.20</v>
       </c>
       <c r="AI69" t="s">
         <v>17</v>
@@ -8955,19 +9015,19 @@
     </row>
     <row r="70" spans="1:38">
       <c r="A70" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B70" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C70" t="s">
         <v>2</v>
       </c>
       <c r="D70" s="2">
-        <v>46141</v>
+        <v>46139</v>
       </c>
       <c r="E70" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="F70" t="s">
         <v>1</v>
@@ -8988,10 +9048,10 @@
         <v>40</v>
       </c>
       <c r="L70" t="s">
-        <v>148</v>
+        <v>41</v>
       </c>
       <c r="M70" t="s">
-        <v>149</v>
+        <v>42</v>
       </c>
       <c r="N70" t="s">
         <v>9</v>
@@ -9003,46 +9063,46 @@
         <v>9</v>
       </c>
       <c r="Q70" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="R70" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="S70" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="T70" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="U70" t="s">
         <v>45</v>
       </c>
       <c r="V70" s="3">
-        <v>195000.000</v>
+        <v>217000.000</v>
       </c>
       <c r="W70" s="3">
-        <v>99950.000</v>
+        <v>216860.000</v>
       </c>
       <c r="X70" s="3">
-        <v>95050.000</v>
+        <v>0.000</v>
       </c>
       <c r="Y70" t="s">
         <v>15</v>
       </c>
       <c r="Z70" s="2">
-        <v>46181</v>
+        <v>46147</v>
       </c>
       <c r="AA70" s="2">
-        <v>46149</v>
+        <v>46200</v>
       </c>
       <c r="AB70" s="2">
         <v>46143</v>
       </c>
       <c r="AC70" s="4">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="AD70" s="5">
-        <v>14.50</v>
+        <v>15.35</v>
       </c>
       <c r="AE70" t="s">
         <v>16</v>
@@ -9051,13 +9111,13 @@
         <v>1</v>
       </c>
       <c r="AG70" s="5">
-        <v>2827500.00</v>
+        <v>3330950.00</v>
       </c>
       <c r="AH70" s="5">
-        <v>1449275.00</v>
+        <v>3328801.00</v>
       </c>
       <c r="AI70" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AJ70" t="s">
         <v>9</v>
@@ -9071,10 +9131,10 @@
     </row>
     <row r="71" spans="1:38">
       <c r="A71" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B71" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C71" t="s">
         <v>2</v>
@@ -9083,13 +9143,13 @@
         <v>46141</v>
       </c>
       <c r="E71" t="s">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="F71" t="s">
         <v>1</v>
       </c>
       <c r="G71" s="2">
-        <v>46134</v>
+        <v>45997</v>
       </c>
       <c r="H71" s="2">
         <v>46141</v>
@@ -9104,10 +9164,10 @@
         <v>40</v>
       </c>
       <c r="L71" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="M71" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="N71" t="s">
         <v>9</v>
@@ -9134,18 +9194,20 @@
         <v>45</v>
       </c>
       <c r="V71" s="3">
-        <v>310000.000</v>
+        <v>80000.000</v>
       </c>
       <c r="W71" s="3">
+        <v>80000.000</v>
+      </c>
+      <c r="X71" s="3">
         <v>0.000</v>
-      </c>
-      <c r="X71" s="3">
-        <v>310000.000</v>
       </c>
       <c r="Y71" t="s">
         <v>15</v>
       </c>
-      <c r="Z71" s="2"/>
+      <c r="Z71" s="2">
+        <v>46163</v>
+      </c>
       <c r="AA71" s="2">
         <v>46149</v>
       </c>
@@ -9153,7 +9215,7 @@
         <v>46143</v>
       </c>
       <c r="AC71" s="4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AD71" s="5">
         <v>14.50</v>
@@ -9165,13 +9227,13 @@
         <v>1</v>
       </c>
       <c r="AG71" s="5">
-        <v>4495000.00</v>
+        <v>1160000.00</v>
       </c>
       <c r="AH71" s="5">
-        <v>0.00</v>
+        <v>1160000.00</v>
       </c>
       <c r="AI71" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AJ71" t="s">
         <v>9</v>
@@ -9185,10 +9247,10 @@
     </row>
     <row r="72" spans="1:38">
       <c r="A72" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B72" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="C72" t="s">
         <v>2</v>
@@ -9197,16 +9259,16 @@
         <v>46141</v>
       </c>
       <c r="E72" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="F72" t="s">
         <v>1</v>
       </c>
       <c r="G72" s="2">
-        <v>46134</v>
+        <v>45997</v>
       </c>
       <c r="H72" s="2">
-        <v>46141</v>
+        <v>46135</v>
       </c>
       <c r="I72" t="s">
         <v>4</v>
@@ -9218,10 +9280,10 @@
         <v>40</v>
       </c>
       <c r="L72" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="M72" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="N72" t="s">
         <v>9</v>
@@ -9248,18 +9310,20 @@
         <v>45</v>
       </c>
       <c r="V72" s="3">
-        <v>310000.000</v>
+        <v>195000.000</v>
       </c>
       <c r="W72" s="3">
-        <v>0.000</v>
+        <v>99950.000</v>
       </c>
       <c r="X72" s="3">
-        <v>310000.000</v>
+        <v>95050.000</v>
       </c>
       <c r="Y72" t="s">
         <v>15</v>
       </c>
-      <c r="Z72" s="2"/>
+      <c r="Z72" s="2">
+        <v>46181</v>
+      </c>
       <c r="AA72" s="2">
         <v>46149</v>
       </c>
@@ -9267,7 +9331,7 @@
         <v>46143</v>
       </c>
       <c r="AC72" s="4">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AD72" s="5">
         <v>14.50</v>
@@ -9279,10 +9343,10 @@
         <v>1</v>
       </c>
       <c r="AG72" s="5">
-        <v>4495000.00</v>
+        <v>2827500.00</v>
       </c>
       <c r="AH72" s="5">
-        <v>0.00</v>
+        <v>1449275.00</v>
       </c>
       <c r="AI72" t="s">
         <v>9</v>
@@ -9299,10 +9363,10 @@
     </row>
     <row r="73" spans="1:38">
       <c r="A73" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B73" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="C73" t="s">
         <v>2</v>
@@ -9311,7 +9375,7 @@
         <v>46141</v>
       </c>
       <c r="E73" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="F73" t="s">
         <v>1</v>
@@ -9332,10 +9396,10 @@
         <v>40</v>
       </c>
       <c r="L73" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="M73" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="N73" t="s">
         <v>9</v>
@@ -9365,17 +9429,15 @@
         <v>310000.000</v>
       </c>
       <c r="W73" s="3">
-        <v>299710.000</v>
+        <v>0.000</v>
       </c>
       <c r="X73" s="3">
-        <v>10290.000</v>
+        <v>310000.000</v>
       </c>
       <c r="Y73" t="s">
         <v>15</v>
       </c>
-      <c r="Z73" s="2">
-        <v>46158</v>
-      </c>
+      <c r="Z73" s="2"/>
       <c r="AA73" s="2">
         <v>46149</v>
       </c>
@@ -9383,7 +9445,7 @@
         <v>46143</v>
       </c>
       <c r="AC73" s="4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AD73" s="5">
         <v>14.50</v>
@@ -9398,7 +9460,7 @@
         <v>4495000.00</v>
       </c>
       <c r="AH73" s="5">
-        <v>4345795.00</v>
+        <v>0.00</v>
       </c>
       <c r="AI73" t="s">
         <v>9</v>
@@ -9415,10 +9477,10 @@
     </row>
     <row r="74" spans="1:38">
       <c r="A74" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B74" t="s">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="C74" t="s">
         <v>2</v>
@@ -9427,7 +9489,7 @@
         <v>46141</v>
       </c>
       <c r="E74" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="F74" t="s">
         <v>1</v>
@@ -9448,10 +9510,10 @@
         <v>40</v>
       </c>
       <c r="L74" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="M74" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="N74" t="s">
         <v>9</v>
@@ -9469,7 +9531,7 @@
         <v>64</v>
       </c>
       <c r="S74" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T74" t="s">
         <v>13</v>
@@ -9478,20 +9540,18 @@
         <v>45</v>
       </c>
       <c r="V74" s="3">
-        <v>270000.000</v>
+        <v>310000.000</v>
       </c>
       <c r="W74" s="3">
-        <v>237650.000</v>
+        <v>0.000</v>
       </c>
       <c r="X74" s="3">
-        <v>32350.000</v>
+        <v>310000.000</v>
       </c>
       <c r="Y74" t="s">
         <v>15</v>
       </c>
-      <c r="Z74" s="2">
-        <v>46153</v>
-      </c>
+      <c r="Z74" s="2"/>
       <c r="AA74" s="2">
         <v>46149</v>
       </c>
@@ -9499,7 +9559,7 @@
         <v>46143</v>
       </c>
       <c r="AC74" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AD74" s="5">
         <v>14.50</v>
@@ -9511,10 +9571,10 @@
         <v>1</v>
       </c>
       <c r="AG74" s="5">
-        <v>3915000.00</v>
+        <v>4495000.00</v>
       </c>
       <c r="AH74" s="5">
-        <v>3445925.00</v>
+        <v>0.00</v>
       </c>
       <c r="AI74" t="s">
         <v>9</v>
@@ -9531,10 +9591,10 @@
     </row>
     <row r="75" spans="1:38">
       <c r="A75" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B75" t="s">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="C75" t="s">
         <v>2</v>
@@ -9543,7 +9603,7 @@
         <v>46141</v>
       </c>
       <c r="E75" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F75" t="s">
         <v>1</v>
@@ -9564,10 +9624,10 @@
         <v>40</v>
       </c>
       <c r="L75" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="M75" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="N75" t="s">
         <v>9</v>
@@ -9585,7 +9645,7 @@
         <v>64</v>
       </c>
       <c r="S75" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T75" t="s">
         <v>13</v>
@@ -9594,18 +9654,20 @@
         <v>45</v>
       </c>
       <c r="V75" s="3">
-        <v>90000.000</v>
+        <v>310000.000</v>
       </c>
       <c r="W75" s="3">
-        <v>0.000</v>
+        <v>299710.000</v>
       </c>
       <c r="X75" s="3">
-        <v>90000.000</v>
+        <v>10290.000</v>
       </c>
       <c r="Y75" t="s">
         <v>15</v>
       </c>
-      <c r="Z75" s="2"/>
+      <c r="Z75" s="2">
+        <v>46158</v>
+      </c>
       <c r="AA75" s="2">
         <v>46149</v>
       </c>
@@ -9613,7 +9675,7 @@
         <v>46143</v>
       </c>
       <c r="AC75" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AD75" s="5">
         <v>14.50</v>
@@ -9625,10 +9687,10 @@
         <v>1</v>
       </c>
       <c r="AG75" s="5">
-        <v>1305000.00</v>
+        <v>4495000.00</v>
       </c>
       <c r="AH75" s="5">
-        <v>0.00</v>
+        <v>4345795.00</v>
       </c>
       <c r="AI75" t="s">
         <v>9</v>
@@ -9645,7 +9707,7 @@
     </row>
     <row r="76" spans="1:38">
       <c r="A76" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B76" t="s">
         <v>1</v>
@@ -9657,16 +9719,16 @@
         <v>46141</v>
       </c>
       <c r="E76" t="s">
-        <v>123</v>
+        <v>163</v>
       </c>
       <c r="F76" t="s">
         <v>1</v>
       </c>
       <c r="G76" s="2">
-        <v>45986</v>
+        <v>46134</v>
       </c>
       <c r="H76" s="2">
-        <v>46115</v>
+        <v>46141</v>
       </c>
       <c r="I76" t="s">
         <v>4</v>
@@ -9678,10 +9740,10 @@
         <v>40</v>
       </c>
       <c r="L76" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="M76" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="N76" t="s">
         <v>9</v>
@@ -9699,7 +9761,7 @@
         <v>64</v>
       </c>
       <c r="S76" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="T76" t="s">
         <v>13</v>
@@ -9708,19 +9770,19 @@
         <v>45</v>
       </c>
       <c r="V76" s="3">
-        <v>10000.000</v>
+        <v>270000.000</v>
       </c>
       <c r="W76" s="3">
-        <v>10000.000</v>
+        <v>237650.000</v>
       </c>
       <c r="X76" s="3">
-        <v>0.000</v>
+        <v>32350.000</v>
       </c>
       <c r="Y76" t="s">
         <v>15</v>
       </c>
       <c r="Z76" s="2">
-        <v>46163</v>
+        <v>46153</v>
       </c>
       <c r="AA76" s="2">
         <v>46149</v>
@@ -9729,7 +9791,7 @@
         <v>46143</v>
       </c>
       <c r="AC76" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AD76" s="5">
         <v>14.50</v>
@@ -9741,13 +9803,13 @@
         <v>1</v>
       </c>
       <c r="AG76" s="5">
-        <v>145000.00</v>
+        <v>3915000.00</v>
       </c>
       <c r="AH76" s="5">
-        <v>145000.00</v>
+        <v>3445925.00</v>
       </c>
       <c r="AI76" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AJ76" t="s">
         <v>9</v>
@@ -9761,7 +9823,7 @@
     </row>
     <row r="77" spans="1:38">
       <c r="A77" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B77" t="s">
         <v>19</v>
@@ -9773,13 +9835,13 @@
         <v>46141</v>
       </c>
       <c r="E77" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F77" t="s">
         <v>1</v>
       </c>
       <c r="G77" s="2">
-        <v>45997</v>
+        <v>46134</v>
       </c>
       <c r="H77" s="2">
         <v>46141</v>
@@ -9794,10 +9856,10 @@
         <v>40</v>
       </c>
       <c r="L77" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="M77" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="N77" t="s">
         <v>9</v>
@@ -9815,7 +9877,7 @@
         <v>64</v>
       </c>
       <c r="S77" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="T77" t="s">
         <v>13</v>
@@ -9824,20 +9886,18 @@
         <v>45</v>
       </c>
       <c r="V77" s="3">
-        <v>260000.000</v>
+        <v>90000.000</v>
       </c>
       <c r="W77" s="3">
-        <v>229970.000</v>
+        <v>0.000</v>
       </c>
       <c r="X77" s="3">
-        <v>30030.000</v>
+        <v>90000.000</v>
       </c>
       <c r="Y77" t="s">
         <v>15</v>
       </c>
-      <c r="Z77" s="2">
-        <v>46163</v>
-      </c>
+      <c r="Z77" s="2"/>
       <c r="AA77" s="2">
         <v>46149</v>
       </c>
@@ -9845,7 +9905,7 @@
         <v>46143</v>
       </c>
       <c r="AC77" s="4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AD77" s="5">
         <v>14.50</v>
@@ -9857,10 +9917,10 @@
         <v>1</v>
       </c>
       <c r="AG77" s="5">
-        <v>3770000.00</v>
+        <v>1305000.00</v>
       </c>
       <c r="AH77" s="5">
-        <v>3334565.00</v>
+        <v>0.00</v>
       </c>
       <c r="AI77" t="s">
         <v>9</v>
@@ -9877,10 +9937,10 @@
     </row>
     <row r="78" spans="1:38">
       <c r="A78" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B78" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C78" t="s">
         <v>2</v>
@@ -9889,16 +9949,16 @@
         <v>46141</v>
       </c>
       <c r="E78" t="s">
-        <v>158</v>
+        <v>123</v>
       </c>
       <c r="F78" t="s">
         <v>1</v>
       </c>
       <c r="G78" s="2">
-        <v>46134</v>
+        <v>45986</v>
       </c>
       <c r="H78" s="2">
-        <v>46141</v>
+        <v>46115</v>
       </c>
       <c r="I78" t="s">
         <v>4</v>
@@ -9910,10 +9970,10 @@
         <v>40</v>
       </c>
       <c r="L78" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="M78" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="N78" t="s">
         <v>9</v>
@@ -9940,19 +10000,19 @@
         <v>45</v>
       </c>
       <c r="V78" s="3">
-        <v>240000.000</v>
+        <v>10000.000</v>
       </c>
       <c r="W78" s="3">
-        <v>30040.000</v>
+        <v>10000.000</v>
       </c>
       <c r="X78" s="3">
-        <v>209960.000</v>
+        <v>0.000</v>
       </c>
       <c r="Y78" t="s">
         <v>15</v>
       </c>
       <c r="Z78" s="2">
-        <v>46213</v>
+        <v>46163</v>
       </c>
       <c r="AA78" s="2">
         <v>46149</v>
@@ -9961,7 +10021,7 @@
         <v>46143</v>
       </c>
       <c r="AC78" s="4">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="AD78" s="5">
         <v>14.50</v>
@@ -9973,13 +10033,13 @@
         <v>1</v>
       </c>
       <c r="AG78" s="5">
-        <v>3480000.00</v>
+        <v>145000.00</v>
       </c>
       <c r="AH78" s="5">
-        <v>435580.00</v>
+        <v>145000.00</v>
       </c>
       <c r="AI78" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AJ78" t="s">
         <v>9</v>
@@ -9993,10 +10053,10 @@
     </row>
     <row r="79" spans="1:38">
       <c r="A79" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B79" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="C79" t="s">
         <v>2</v>
@@ -10005,13 +10065,13 @@
         <v>46141</v>
       </c>
       <c r="E79" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="F79" t="s">
         <v>1</v>
       </c>
       <c r="G79" s="2">
-        <v>46134</v>
+        <v>45997</v>
       </c>
       <c r="H79" s="2">
         <v>46141</v>
@@ -10026,10 +10086,10 @@
         <v>40</v>
       </c>
       <c r="L79" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="M79" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="N79" t="s">
         <v>9</v>
@@ -10056,18 +10116,20 @@
         <v>45</v>
       </c>
       <c r="V79" s="3">
-        <v>150000.000</v>
+        <v>260000.000</v>
       </c>
       <c r="W79" s="3">
-        <v>0.000</v>
+        <v>229970.000</v>
       </c>
       <c r="X79" s="3">
-        <v>150000.000</v>
+        <v>30030.000</v>
       </c>
       <c r="Y79" t="s">
         <v>15</v>
       </c>
-      <c r="Z79" s="2"/>
+      <c r="Z79" s="2">
+        <v>46163</v>
+      </c>
       <c r="AA79" s="2">
         <v>46149</v>
       </c>
@@ -10075,7 +10137,7 @@
         <v>46143</v>
       </c>
       <c r="AC79" s="4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AD79" s="5">
         <v>14.50</v>
@@ -10087,10 +10149,10 @@
         <v>1</v>
       </c>
       <c r="AG79" s="5">
-        <v>2175000.00</v>
+        <v>3770000.00</v>
       </c>
       <c r="AH79" s="5">
-        <v>0.00</v>
+        <v>3334565.00</v>
       </c>
       <c r="AI79" t="s">
         <v>9</v>
@@ -10107,10 +10169,10 @@
     </row>
     <row r="80" spans="1:38">
       <c r="A80" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B80" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C80" t="s">
         <v>2</v>
@@ -10119,13 +10181,13 @@
         <v>46141</v>
       </c>
       <c r="E80" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="F80" t="s">
         <v>1</v>
       </c>
       <c r="G80" s="2">
-        <v>45814</v>
+        <v>46134</v>
       </c>
       <c r="H80" s="2">
         <v>46141</v>
@@ -10140,10 +10202,10 @@
         <v>40</v>
       </c>
       <c r="L80" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="M80" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="N80" t="s">
         <v>9</v>
@@ -10161,7 +10223,7 @@
         <v>64</v>
       </c>
       <c r="S80" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="T80" t="s">
         <v>13</v>
@@ -10170,19 +10232,19 @@
         <v>45</v>
       </c>
       <c r="V80" s="3">
-        <v>25000.000</v>
+        <v>240000.000</v>
       </c>
       <c r="W80" s="3">
-        <v>25000.000</v>
+        <v>30040.000</v>
       </c>
       <c r="X80" s="3">
-        <v>0.000</v>
+        <v>209960.000</v>
       </c>
       <c r="Y80" t="s">
         <v>15</v>
       </c>
       <c r="Z80" s="2">
-        <v>46167</v>
+        <v>46213</v>
       </c>
       <c r="AA80" s="2">
         <v>46149</v>
@@ -10191,7 +10253,7 @@
         <v>46143</v>
       </c>
       <c r="AC80" s="4">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="AD80" s="5">
         <v>14.50</v>
@@ -10203,13 +10265,13 @@
         <v>1</v>
       </c>
       <c r="AG80" s="5">
-        <v>362500.00</v>
+        <v>3480000.00</v>
       </c>
       <c r="AH80" s="5">
-        <v>362500.00</v>
+        <v>435580.00</v>
       </c>
       <c r="AI80" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AJ80" t="s">
         <v>9</v>
@@ -10223,10 +10285,10 @@
     </row>
     <row r="81" spans="1:38">
       <c r="A81" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B81" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="C81" t="s">
         <v>2</v>
@@ -10235,16 +10297,16 @@
         <v>46141</v>
       </c>
       <c r="E81" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="F81" t="s">
         <v>1</v>
       </c>
       <c r="G81" s="2">
-        <v>45997</v>
+        <v>46134</v>
       </c>
       <c r="H81" s="2">
-        <v>46115</v>
+        <v>46141</v>
       </c>
       <c r="I81" t="s">
         <v>4</v>
@@ -10256,10 +10318,10 @@
         <v>40</v>
       </c>
       <c r="L81" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="M81" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="N81" t="s">
         <v>9</v>
@@ -10277,7 +10339,7 @@
         <v>64</v>
       </c>
       <c r="S81" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="T81" t="s">
         <v>13</v>
@@ -10286,20 +10348,18 @@
         <v>45</v>
       </c>
       <c r="V81" s="3">
-        <v>39000.000</v>
+        <v>150000.000</v>
       </c>
       <c r="W81" s="3">
-        <v>31070.000</v>
+        <v>0.000</v>
       </c>
       <c r="X81" s="3">
-        <v>7930.000</v>
+        <v>150000.000</v>
       </c>
       <c r="Y81" t="s">
         <v>15</v>
       </c>
-      <c r="Z81" s="2">
-        <v>46167</v>
-      </c>
+      <c r="Z81" s="2"/>
       <c r="AA81" s="2">
         <v>46149</v>
       </c>
@@ -10307,7 +10367,7 @@
         <v>46143</v>
       </c>
       <c r="AC81" s="4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AD81" s="5">
         <v>14.50</v>
@@ -10319,10 +10379,10 @@
         <v>1</v>
       </c>
       <c r="AG81" s="5">
-        <v>565500.00</v>
+        <v>2175000.00</v>
       </c>
       <c r="AH81" s="5">
-        <v>450515.00</v>
+        <v>0.00</v>
       </c>
       <c r="AI81" t="s">
         <v>9</v>
@@ -10339,10 +10399,10 @@
     </row>
     <row r="82" spans="1:38">
       <c r="A82" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B82" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C82" t="s">
         <v>2</v>
@@ -10351,13 +10411,13 @@
         <v>46141</v>
       </c>
       <c r="E82" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="F82" t="s">
         <v>1</v>
       </c>
       <c r="G82" s="2">
-        <v>46134</v>
+        <v>45814</v>
       </c>
       <c r="H82" s="2">
         <v>46141</v>
@@ -10372,10 +10432,10 @@
         <v>40</v>
       </c>
       <c r="L82" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="M82" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="N82" t="s">
         <v>9</v>
@@ -10402,19 +10462,19 @@
         <v>45</v>
       </c>
       <c r="V82" s="3">
-        <v>208000.000</v>
+        <v>25000.000</v>
       </c>
       <c r="W82" s="3">
-        <v>28030.000</v>
+        <v>25000.000</v>
       </c>
       <c r="X82" s="3">
-        <v>179970.000</v>
+        <v>0.000</v>
       </c>
       <c r="Y82" t="s">
         <v>15</v>
       </c>
       <c r="Z82" s="2">
-        <v>46209</v>
+        <v>46167</v>
       </c>
       <c r="AA82" s="2">
         <v>46149</v>
@@ -10423,7 +10483,7 @@
         <v>46143</v>
       </c>
       <c r="AC82" s="4">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="AD82" s="5">
         <v>14.50</v>
@@ -10435,13 +10495,13 @@
         <v>1</v>
       </c>
       <c r="AG82" s="5">
-        <v>3016000.00</v>
+        <v>362500.00</v>
       </c>
       <c r="AH82" s="5">
-        <v>406435.00</v>
+        <v>362500.00</v>
       </c>
       <c r="AI82" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AJ82" t="s">
         <v>9</v>
@@ -10455,10 +10515,10 @@
     </row>
     <row r="83" spans="1:38">
       <c r="A83" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B83" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="C83" t="s">
         <v>2</v>
@@ -10467,16 +10527,16 @@
         <v>46141</v>
       </c>
       <c r="E83" t="s">
-        <v>163</v>
+        <v>70</v>
       </c>
       <c r="F83" t="s">
         <v>1</v>
       </c>
       <c r="G83" s="2">
-        <v>46134</v>
+        <v>45997</v>
       </c>
       <c r="H83" s="2">
-        <v>46141</v>
+        <v>46115</v>
       </c>
       <c r="I83" t="s">
         <v>4</v>
@@ -10488,10 +10548,10 @@
         <v>40</v>
       </c>
       <c r="L83" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="M83" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="N83" t="s">
         <v>9</v>
@@ -10518,19 +10578,19 @@
         <v>45</v>
       </c>
       <c r="V83" s="3">
-        <v>148000.000</v>
+        <v>39000.000</v>
       </c>
       <c r="W83" s="3">
-        <v>28030.000</v>
+        <v>31070.000</v>
       </c>
       <c r="X83" s="3">
-        <v>119970.000</v>
+        <v>7930.000</v>
       </c>
       <c r="Y83" t="s">
         <v>15</v>
       </c>
       <c r="Z83" s="2">
-        <v>46203</v>
+        <v>46167</v>
       </c>
       <c r="AA83" s="2">
         <v>46149</v>
@@ -10539,7 +10599,7 @@
         <v>46143</v>
       </c>
       <c r="AC83" s="4">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="AD83" s="5">
         <v>14.50</v>
@@ -10551,10 +10611,10 @@
         <v>1</v>
       </c>
       <c r="AG83" s="5">
-        <v>2146000.00</v>
+        <v>565500.00</v>
       </c>
       <c r="AH83" s="5">
-        <v>406435.00</v>
+        <v>450515.00</v>
       </c>
       <c r="AI83" t="s">
         <v>9</v>
@@ -10571,10 +10631,10 @@
     </row>
     <row r="84" spans="1:38">
       <c r="A84" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B84" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C84" t="s">
         <v>2</v>
@@ -10583,13 +10643,13 @@
         <v>46141</v>
       </c>
       <c r="E84" t="s">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="F84" t="s">
         <v>1</v>
       </c>
       <c r="G84" s="2">
-        <v>45997</v>
+        <v>46134</v>
       </c>
       <c r="H84" s="2">
         <v>46141</v>
@@ -10604,10 +10664,10 @@
         <v>40</v>
       </c>
       <c r="L84" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="M84" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="N84" t="s">
         <v>9</v>
@@ -10625,7 +10685,7 @@
         <v>64</v>
       </c>
       <c r="S84" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="T84" t="s">
         <v>13</v>
@@ -10634,31 +10694,31 @@
         <v>45</v>
       </c>
       <c r="V84" s="3">
-        <v>60000.000</v>
+        <v>208000.000</v>
       </c>
       <c r="W84" s="3">
-        <v>50000.000</v>
+        <v>28030.000</v>
       </c>
       <c r="X84" s="3">
-        <v>10000.000</v>
+        <v>179970.000</v>
       </c>
       <c r="Y84" t="s">
         <v>15</v>
       </c>
       <c r="Z84" s="2">
-        <v>46161</v>
+        <v>46209</v>
       </c>
       <c r="AA84" s="2">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="AB84" s="2">
         <v>46143</v>
       </c>
       <c r="AC84" s="4">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="AD84" s="5">
-        <v>15.75</v>
+        <v>14.50</v>
       </c>
       <c r="AE84" t="s">
         <v>16</v>
@@ -10667,10 +10727,10 @@
         <v>1</v>
       </c>
       <c r="AG84" s="5">
-        <v>945000.00</v>
+        <v>3016000.00</v>
       </c>
       <c r="AH84" s="5">
-        <v>787500.00</v>
+        <v>406435.00</v>
       </c>
       <c r="AI84" t="s">
         <v>9</v>
@@ -10687,10 +10747,10 @@
     </row>
     <row r="85" spans="1:38">
       <c r="A85" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B85" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="C85" t="s">
         <v>2</v>
@@ -10699,7 +10759,7 @@
         <v>46141</v>
       </c>
       <c r="E85" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="F85" t="s">
         <v>1</v>
@@ -10720,10 +10780,10 @@
         <v>40</v>
       </c>
       <c r="L85" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="M85" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="N85" t="s">
         <v>9</v>
@@ -10741,7 +10801,7 @@
         <v>64</v>
       </c>
       <c r="S85" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="T85" t="s">
         <v>13</v>
@@ -10750,29 +10810,31 @@
         <v>45</v>
       </c>
       <c r="V85" s="3">
-        <v>140000.000</v>
+        <v>148000.000</v>
       </c>
       <c r="W85" s="3">
-        <v>0.000</v>
+        <v>28030.000</v>
       </c>
       <c r="X85" s="3">
-        <v>140000.000</v>
+        <v>119970.000</v>
       </c>
       <c r="Y85" t="s">
         <v>15</v>
       </c>
-      <c r="Z85" s="2"/>
+      <c r="Z85" s="2">
+        <v>46203</v>
+      </c>
       <c r="AA85" s="2">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="AB85" s="2">
         <v>46143</v>
       </c>
       <c r="AC85" s="4">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AD85" s="5">
-        <v>15.75</v>
+        <v>14.50</v>
       </c>
       <c r="AE85" t="s">
         <v>16</v>
@@ -10781,10 +10843,10 @@
         <v>1</v>
       </c>
       <c r="AG85" s="5">
-        <v>2205000.00</v>
+        <v>2146000.00</v>
       </c>
       <c r="AH85" s="5">
-        <v>0.00</v>
+        <v>406435.00</v>
       </c>
       <c r="AI85" t="s">
         <v>9</v>
@@ -10801,7 +10863,7 @@
     </row>
     <row r="86" spans="1:38">
       <c r="A86" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B86" t="s">
         <v>1</v>
@@ -10810,10 +10872,10 @@
         <v>2</v>
       </c>
       <c r="D86" s="2">
-        <v>46142</v>
+        <v>46141</v>
       </c>
       <c r="E86" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="F86" t="s">
         <v>1</v>
@@ -10834,10 +10896,10 @@
         <v>40</v>
       </c>
       <c r="L86" t="s">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="M86" t="s">
-        <v>62</v>
+        <v>158</v>
       </c>
       <c r="N86" t="s">
         <v>9</v>
@@ -10855,7 +10917,7 @@
         <v>64</v>
       </c>
       <c r="S86" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="T86" t="s">
         <v>13</v>
@@ -10864,31 +10926,31 @@
         <v>45</v>
       </c>
       <c r="V86" s="3">
-        <v>40000.000</v>
+        <v>60000.000</v>
       </c>
       <c r="W86" s="3">
-        <v>40000.000</v>
+        <v>50000.000</v>
       </c>
       <c r="X86" s="3">
-        <v>0.000</v>
+        <v>10000.000</v>
       </c>
       <c r="Y86" t="s">
         <v>15</v>
       </c>
       <c r="Z86" s="2">
-        <v>46143</v>
+        <v>46161</v>
       </c>
       <c r="AA86" s="2">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="AB86" s="2">
         <v>46143</v>
       </c>
       <c r="AC86" s="4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AD86" s="5">
-        <v>14.84</v>
+        <v>15.75</v>
       </c>
       <c r="AE86" t="s">
         <v>16</v>
@@ -10897,13 +10959,13 @@
         <v>1</v>
       </c>
       <c r="AG86" s="5">
-        <v>593600.00</v>
+        <v>945000.00</v>
       </c>
       <c r="AH86" s="5">
-        <v>593600.00</v>
+        <v>787500.00</v>
       </c>
       <c r="AI86" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AJ86" t="s">
         <v>9</v>
@@ -10917,7 +10979,7 @@
     </row>
     <row r="87" spans="1:38">
       <c r="A87" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B87" t="s">
         <v>19</v>
@@ -10926,19 +10988,19 @@
         <v>2</v>
       </c>
       <c r="D87" s="2">
-        <v>46142</v>
+        <v>46141</v>
       </c>
       <c r="E87" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="F87" t="s">
         <v>1</v>
       </c>
       <c r="G87" s="2">
-        <v>45997</v>
+        <v>46134</v>
       </c>
       <c r="H87" s="2">
-        <v>46142</v>
+        <v>46141</v>
       </c>
       <c r="I87" t="s">
         <v>4</v>
@@ -10950,10 +11012,10 @@
         <v>40</v>
       </c>
       <c r="L87" t="s">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="M87" t="s">
-        <v>62</v>
+        <v>158</v>
       </c>
       <c r="N87" t="s">
         <v>9</v>
@@ -10971,7 +11033,7 @@
         <v>64</v>
       </c>
       <c r="S87" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="T87" t="s">
         <v>13</v>
@@ -10980,31 +11042,29 @@
         <v>45</v>
       </c>
       <c r="V87" s="3">
-        <v>200000.000</v>
+        <v>140000.000</v>
       </c>
       <c r="W87" s="3">
-        <v>200000.000</v>
+        <v>0.000</v>
       </c>
       <c r="X87" s="3">
-        <v>0.000</v>
+        <v>140000.000</v>
       </c>
       <c r="Y87" t="s">
         <v>15</v>
       </c>
-      <c r="Z87" s="2">
+      <c r="Z87" s="2"/>
+      <c r="AA87" s="2">
         <v>46146</v>
-      </c>
-      <c r="AA87" s="2">
-        <v>46147</v>
       </c>
       <c r="AB87" s="2">
         <v>46143</v>
       </c>
       <c r="AC87" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD87" s="5">
-        <v>14.84</v>
+        <v>15.75</v>
       </c>
       <c r="AE87" t="s">
         <v>16</v>
@@ -11013,13 +11073,13 @@
         <v>1</v>
       </c>
       <c r="AG87" s="5">
-        <v>2968000.00</v>
+        <v>2205000.00</v>
       </c>
       <c r="AH87" s="5">
-        <v>2968000.00</v>
+        <v>0.00</v>
       </c>
       <c r="AI87" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AJ87" t="s">
         <v>9</v>
@@ -11033,7 +11093,7 @@
     </row>
     <row r="88" spans="1:38">
       <c r="A88" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B88" t="s">
         <v>1</v>
@@ -11042,19 +11102,19 @@
         <v>2</v>
       </c>
       <c r="D88" s="2">
-        <v>46144</v>
+        <v>46142</v>
       </c>
       <c r="E88" t="s">
-        <v>169</v>
+        <v>60</v>
       </c>
       <c r="F88" t="s">
         <v>1</v>
       </c>
       <c r="G88" s="2">
-        <v>46134</v>
+        <v>45997</v>
       </c>
       <c r="H88" s="2">
-        <v>46144</v>
+        <v>46141</v>
       </c>
       <c r="I88" t="s">
         <v>4</v>
@@ -11096,10 +11156,10 @@
         <v>45</v>
       </c>
       <c r="V88" s="3">
-        <v>2260.000</v>
+        <v>40000.000</v>
       </c>
       <c r="W88" s="3">
-        <v>2260.000</v>
+        <v>40000.000</v>
       </c>
       <c r="X88" s="3">
         <v>0.000</v>
@@ -11108,19 +11168,19 @@
         <v>15</v>
       </c>
       <c r="Z88" s="2">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="AA88" s="2">
         <v>46147</v>
       </c>
       <c r="AB88" s="2">
-        <v>46145</v>
+        <v>46143</v>
       </c>
       <c r="AC88" s="4">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AD88" s="5">
-        <v>13.50</v>
+        <v>14.84</v>
       </c>
       <c r="AE88" t="s">
         <v>16</v>
@@ -11129,10 +11189,10 @@
         <v>1</v>
       </c>
       <c r="AG88" s="5">
-        <v>30510.00</v>
+        <v>593600.00</v>
       </c>
       <c r="AH88" s="5">
-        <v>30510.00</v>
+        <v>593600.00</v>
       </c>
       <c r="AI88" t="s">
         <v>17</v>
@@ -11149,28 +11209,28 @@
     </row>
     <row r="89" spans="1:38">
       <c r="A89" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B89" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C89" t="s">
         <v>2</v>
       </c>
       <c r="D89" s="2">
-        <v>46150</v>
+        <v>46142</v>
       </c>
       <c r="E89" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="F89" t="s">
         <v>1</v>
       </c>
       <c r="G89" s="2">
-        <v>46134</v>
+        <v>45997</v>
       </c>
       <c r="H89" s="2">
-        <v>46144</v>
+        <v>46142</v>
       </c>
       <c r="I89" t="s">
         <v>4</v>
@@ -11212,10 +11272,10 @@
         <v>45</v>
       </c>
       <c r="V89" s="3">
-        <v>32000.000</v>
+        <v>200000.000</v>
       </c>
       <c r="W89" s="3">
-        <v>28180.000</v>
+        <v>200000.000</v>
       </c>
       <c r="X89" s="3">
         <v>0.000</v>
@@ -11224,16 +11284,16 @@
         <v>15</v>
       </c>
       <c r="Z89" s="2">
-        <v>46157</v>
+        <v>46146</v>
       </c>
       <c r="AA89" s="2">
-        <v>46199</v>
+        <v>46147</v>
       </c>
       <c r="AB89" s="2">
-        <v>46157</v>
+        <v>46143</v>
       </c>
       <c r="AC89" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD89" s="5">
         <v>14.84</v>
@@ -11245,10 +11305,10 @@
         <v>1</v>
       </c>
       <c r="AG89" s="5">
-        <v>474880.00</v>
+        <v>2968000.00</v>
       </c>
       <c r="AH89" s="5">
-        <v>418191.20</v>
+        <v>2968000.00</v>
       </c>
       <c r="AI89" t="s">
         <v>17</v>
@@ -11265,7 +11325,7 @@
     </row>
     <row r="90" spans="1:38">
       <c r="A90" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B90" t="s">
         <v>1</v>
@@ -11274,34 +11334,34 @@
         <v>2</v>
       </c>
       <c r="D90" s="2">
-        <v>46150</v>
+        <v>46144</v>
       </c>
       <c r="E90" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F90" t="s">
         <v>1</v>
       </c>
       <c r="G90" s="2">
-        <v>46073</v>
+        <v>46134</v>
       </c>
       <c r="H90" s="2">
-        <v>46149</v>
+        <v>46144</v>
       </c>
       <c r="I90" t="s">
         <v>4</v>
       </c>
       <c r="J90" t="s">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="K90" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="L90" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="M90" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="N90" t="s">
         <v>9</v>
@@ -11313,25 +11373,25 @@
         <v>9</v>
       </c>
       <c r="Q90" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="R90" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="S90" t="s">
         <v>12</v>
       </c>
       <c r="T90" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="U90" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="V90" s="3">
-        <v>1512.000</v>
+        <v>2260.000</v>
       </c>
       <c r="W90" s="3">
-        <v>1512.000</v>
+        <v>2260.000</v>
       </c>
       <c r="X90" s="3">
         <v>0.000</v>
@@ -11340,19 +11400,19 @@
         <v>15</v>
       </c>
       <c r="Z90" s="2">
-        <v>46164</v>
+        <v>46142</v>
       </c>
       <c r="AA90" s="2">
-        <v>46155</v>
+        <v>46147</v>
       </c>
       <c r="AB90" s="2">
-        <v>46181</v>
+        <v>46145</v>
       </c>
       <c r="AC90" s="4">
-        <v>-17</v>
+        <v>-3</v>
       </c>
       <c r="AD90" s="5">
-        <v>6.66</v>
+        <v>13.50</v>
       </c>
       <c r="AE90" t="s">
         <v>16</v>
@@ -11361,10 +11421,10 @@
         <v>1</v>
       </c>
       <c r="AG90" s="5">
-        <v>10069.92</v>
+        <v>30510.00</v>
       </c>
       <c r="AH90" s="5">
-        <v>10069.92</v>
+        <v>30510.00</v>
       </c>
       <c r="AI90" t="s">
         <v>17</v>
@@ -11381,7 +11441,7 @@
     </row>
     <row r="91" spans="1:38">
       <c r="A91" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B91" t="s">
         <v>1</v>
@@ -11390,34 +11450,34 @@
         <v>2</v>
       </c>
       <c r="D91" s="2">
-        <v>46164</v>
+        <v>46150</v>
       </c>
       <c r="E91" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F91" t="s">
         <v>1</v>
       </c>
       <c r="G91" s="2">
-        <v>46120</v>
+        <v>46134</v>
       </c>
       <c r="H91" s="2">
-        <v>46122</v>
+        <v>46144</v>
       </c>
       <c r="I91" t="s">
         <v>4</v>
       </c>
       <c r="J91" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="K91" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L91" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="M91" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="N91" t="s">
         <v>9</v>
@@ -11429,10 +11489,10 @@
         <v>9</v>
       </c>
       <c r="Q91" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="R91" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="S91" t="s">
         <v>12</v>
@@ -11441,13 +11501,13 @@
         <v>13</v>
       </c>
       <c r="U91" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="V91" s="3">
-        <v>530000.000</v>
+        <v>32000.000</v>
       </c>
       <c r="W91" s="3">
-        <v>360340.000</v>
+        <v>28180.000</v>
       </c>
       <c r="X91" s="3">
         <v>0.000</v>
@@ -11456,19 +11516,19 @@
         <v>15</v>
       </c>
       <c r="Z91" s="2">
-        <v>46163</v>
+        <v>46157</v>
       </c>
       <c r="AA91" s="2">
-        <v>46213</v>
+        <v>46199</v>
       </c>
       <c r="AB91" s="2">
-        <v>46174</v>
+        <v>46157</v>
       </c>
       <c r="AC91" s="4">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="AD91" s="5">
-        <v>5.69</v>
+        <v>14.84</v>
       </c>
       <c r="AE91" t="s">
         <v>16</v>
@@ -11477,10 +11537,10 @@
         <v>1</v>
       </c>
       <c r="AG91" s="5">
-        <v>3015700.00</v>
+        <v>474880.00</v>
       </c>
       <c r="AH91" s="5">
-        <v>2050334.60</v>
+        <v>418191.20</v>
       </c>
       <c r="AI91" t="s">
         <v>17</v>
@@ -11497,7 +11557,7 @@
     </row>
     <row r="92" spans="1:38">
       <c r="A92" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B92" t="s">
         <v>1</v>
@@ -11506,34 +11566,34 @@
         <v>2</v>
       </c>
       <c r="D92" s="2">
-        <v>46164</v>
+        <v>46150</v>
       </c>
       <c r="E92" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="F92" t="s">
         <v>1</v>
       </c>
       <c r="G92" s="2">
-        <v>45997</v>
+        <v>46073</v>
       </c>
       <c r="H92" s="2">
-        <v>46135</v>
+        <v>46149</v>
       </c>
       <c r="I92" t="s">
         <v>4</v>
       </c>
       <c r="J92" t="s">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="K92" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="L92" t="s">
-        <v>41</v>
+        <v>102</v>
       </c>
       <c r="M92" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="N92" t="s">
         <v>9</v>
@@ -11545,46 +11605,46 @@
         <v>9</v>
       </c>
       <c r="Q92" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="R92" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="S92" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="T92" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="U92" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="V92" s="3">
-        <v>30000.000</v>
+        <v>1512.000</v>
       </c>
       <c r="W92" s="3">
-        <v>29980.000</v>
+        <v>1512.000</v>
       </c>
       <c r="X92" s="3">
-        <v>20.000</v>
+        <v>0.000</v>
       </c>
       <c r="Y92" t="s">
         <v>15</v>
       </c>
       <c r="Z92" s="2">
-        <v>46171</v>
+        <v>46164</v>
       </c>
       <c r="AA92" s="2">
-        <v>46169</v>
+        <v>46155</v>
       </c>
       <c r="AB92" s="2">
-        <v>46171</v>
+        <v>46181</v>
       </c>
       <c r="AC92" s="4">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="AD92" s="5">
-        <v>15.42</v>
+        <v>6.66</v>
       </c>
       <c r="AE92" t="s">
         <v>16</v>
@@ -11593,13 +11653,13 @@
         <v>1</v>
       </c>
       <c r="AG92" s="5">
-        <v>462600.00</v>
+        <v>10069.92</v>
       </c>
       <c r="AH92" s="5">
-        <v>462291.60</v>
+        <v>10069.92</v>
       </c>
       <c r="AI92" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AJ92" t="s">
         <v>9</v>
@@ -11613,7 +11673,7 @@
     </row>
     <row r="93" spans="1:38">
       <c r="A93" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B93" t="s">
         <v>1</v>
@@ -11625,31 +11685,31 @@
         <v>46164</v>
       </c>
       <c r="E93" t="s">
-        <v>105</v>
+        <v>183</v>
       </c>
       <c r="F93" t="s">
         <v>1</v>
       </c>
       <c r="G93" s="2">
-        <v>45997</v>
+        <v>46120</v>
       </c>
       <c r="H93" s="2">
-        <v>46072</v>
+        <v>46122</v>
       </c>
       <c r="I93" t="s">
         <v>4</v>
       </c>
       <c r="J93" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="K93" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="L93" t="s">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="M93" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="N93" t="s">
         <v>9</v>
@@ -11661,25 +11721,25 @@
         <v>9</v>
       </c>
       <c r="Q93" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="R93" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="S93" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="T93" t="s">
         <v>13</v>
       </c>
       <c r="U93" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="V93" s="3">
-        <v>20000.000</v>
+        <v>530000.000</v>
       </c>
       <c r="W93" s="3">
-        <v>20000.000</v>
+        <v>360340.000</v>
       </c>
       <c r="X93" s="3">
         <v>0.000</v>
@@ -11688,19 +11748,19 @@
         <v>15</v>
       </c>
       <c r="Z93" s="2">
-        <v>46168</v>
+        <v>46163</v>
       </c>
       <c r="AA93" s="2">
-        <v>46167</v>
+        <v>46213</v>
       </c>
       <c r="AB93" s="2">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="AC93" s="4">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AD93" s="5">
-        <v>16.27</v>
+        <v>5.69</v>
       </c>
       <c r="AE93" t="s">
         <v>16</v>
@@ -11709,10 +11769,10 @@
         <v>1</v>
       </c>
       <c r="AG93" s="5">
-        <v>325400.00</v>
+        <v>3015700.00</v>
       </c>
       <c r="AH93" s="5">
-        <v>325400.00</v>
+        <v>2050334.60</v>
       </c>
       <c r="AI93" t="s">
         <v>17</v>
@@ -11729,10 +11789,10 @@
     </row>
     <row r="94" spans="1:38">
       <c r="A94" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B94" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C94" t="s">
         <v>2</v>
@@ -11741,16 +11801,16 @@
         <v>46164</v>
       </c>
       <c r="E94" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="F94" t="s">
         <v>1</v>
       </c>
       <c r="G94" s="2">
-        <v>46164</v>
+        <v>45997</v>
       </c>
       <c r="H94" s="2">
-        <v>46167</v>
+        <v>46135</v>
       </c>
       <c r="I94" t="s">
         <v>4</v>
@@ -11762,10 +11822,10 @@
         <v>40</v>
       </c>
       <c r="L94" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="M94" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="N94" t="s">
         <v>9</v>
@@ -11783,7 +11843,7 @@
         <v>44</v>
       </c>
       <c r="S94" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="T94" t="s">
         <v>13</v>
@@ -11792,31 +11852,31 @@
         <v>45</v>
       </c>
       <c r="V94" s="3">
-        <v>10000.000</v>
+        <v>30000.000</v>
       </c>
       <c r="W94" s="3">
-        <v>9980.000</v>
+        <v>29980.000</v>
       </c>
       <c r="X94" s="3">
-        <v>0.000</v>
+        <v>20.000</v>
       </c>
       <c r="Y94" t="s">
         <v>15</v>
       </c>
       <c r="Z94" s="2">
-        <v>46168</v>
+        <v>46171</v>
       </c>
       <c r="AA94" s="2">
-        <v>46200</v>
+        <v>46169</v>
       </c>
       <c r="AB94" s="2">
-        <v>46168</v>
+        <v>46171</v>
       </c>
       <c r="AC94" s="4">
         <v>0</v>
       </c>
       <c r="AD94" s="5">
-        <v>16.27</v>
+        <v>15.42</v>
       </c>
       <c r="AE94" t="s">
         <v>16</v>
@@ -11825,13 +11885,13 @@
         <v>1</v>
       </c>
       <c r="AG94" s="5">
-        <v>162700.00</v>
+        <v>462600.00</v>
       </c>
       <c r="AH94" s="5">
-        <v>162374.60</v>
+        <v>462291.60</v>
       </c>
       <c r="AI94" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AJ94" t="s">
         <v>9</v>
@@ -11845,7 +11905,7 @@
     </row>
     <row r="95" spans="1:38">
       <c r="A95" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B95" t="s">
         <v>1</v>
@@ -11854,19 +11914,19 @@
         <v>2</v>
       </c>
       <c r="D95" s="2">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="E95" t="s">
-        <v>169</v>
+        <v>105</v>
       </c>
       <c r="F95" t="s">
         <v>1</v>
       </c>
       <c r="G95" s="2">
-        <v>46134</v>
+        <v>45997</v>
       </c>
       <c r="H95" s="2">
-        <v>46144</v>
+        <v>46072</v>
       </c>
       <c r="I95" t="s">
         <v>4</v>
@@ -11878,10 +11938,10 @@
         <v>40</v>
       </c>
       <c r="L95" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M95" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="N95" t="s">
         <v>9</v>
@@ -11893,13 +11953,13 @@
         <v>9</v>
       </c>
       <c r="Q95" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="R95" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="S95" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="T95" t="s">
         <v>13</v>
@@ -11908,10 +11968,10 @@
         <v>45</v>
       </c>
       <c r="V95" s="3">
-        <v>275740.000</v>
+        <v>20000.000</v>
       </c>
       <c r="W95" s="3">
-        <v>275740.000</v>
+        <v>20000.000</v>
       </c>
       <c r="X95" s="3">
         <v>0.000</v>
@@ -11920,19 +11980,19 @@
         <v>15</v>
       </c>
       <c r="Z95" s="2">
-        <v>46188</v>
+        <v>46168</v>
       </c>
       <c r="AA95" s="2">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="AB95" s="2">
-        <v>46174</v>
+        <v>46168</v>
       </c>
       <c r="AC95" s="4">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AD95" s="5">
-        <v>14.83</v>
+        <v>16.27</v>
       </c>
       <c r="AE95" t="s">
         <v>16</v>
@@ -11941,10 +12001,10 @@
         <v>1</v>
       </c>
       <c r="AG95" s="5">
-        <v>4089224.20</v>
+        <v>325400.00</v>
       </c>
       <c r="AH95" s="5">
-        <v>4089224.20</v>
+        <v>325400.00</v>
       </c>
       <c r="AI95" t="s">
         <v>17</v>
@@ -11961,28 +12021,28 @@
     </row>
     <row r="96" spans="1:38">
       <c r="A96" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B96" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C96" t="s">
         <v>2</v>
       </c>
       <c r="D96" s="2">
+        <v>46164</v>
+      </c>
+      <c r="E96" t="s">
+        <v>186</v>
+      </c>
+      <c r="F96" t="s">
+        <v>1</v>
+      </c>
+      <c r="G96" s="2">
+        <v>46164</v>
+      </c>
+      <c r="H96" s="2">
         <v>46167</v>
-      </c>
-      <c r="E96" t="s">
-        <v>180</v>
-      </c>
-      <c r="F96" t="s">
-        <v>1</v>
-      </c>
-      <c r="G96" s="2">
-        <v>45995</v>
-      </c>
-      <c r="H96" s="2">
-        <v>46106</v>
       </c>
       <c r="I96" t="s">
         <v>4</v>
@@ -11994,10 +12054,10 @@
         <v>40</v>
       </c>
       <c r="L96" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="M96" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="N96" t="s">
         <v>9</v>
@@ -12015,7 +12075,7 @@
         <v>44</v>
       </c>
       <c r="S96" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="T96" t="s">
         <v>13</v>
@@ -12024,10 +12084,10 @@
         <v>45</v>
       </c>
       <c r="V96" s="3">
-        <v>250000.000</v>
+        <v>10000.000</v>
       </c>
       <c r="W96" s="3">
-        <v>250000.000</v>
+        <v>9980.000</v>
       </c>
       <c r="X96" s="3">
         <v>0.000</v>
@@ -12036,19 +12096,19 @@
         <v>15</v>
       </c>
       <c r="Z96" s="2">
-        <v>46177</v>
+        <v>46168</v>
       </c>
       <c r="AA96" s="2">
-        <v>46181</v>
+        <v>46200</v>
       </c>
       <c r="AB96" s="2">
-        <v>46174</v>
+        <v>46168</v>
       </c>
       <c r="AC96" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD96" s="5">
-        <v>15.34</v>
+        <v>16.27</v>
       </c>
       <c r="AE96" t="s">
         <v>16</v>
@@ -12057,10 +12117,10 @@
         <v>1</v>
       </c>
       <c r="AG96" s="5">
-        <v>3835000.00</v>
+        <v>162700.00</v>
       </c>
       <c r="AH96" s="5">
-        <v>3835000.00</v>
+        <v>162374.60</v>
       </c>
       <c r="AI96" t="s">
         <v>17</v>
@@ -12077,10 +12137,10 @@
     </row>
     <row r="97" spans="1:38">
       <c r="A97" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B97" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C97" t="s">
         <v>2</v>
@@ -12089,16 +12149,16 @@
         <v>46167</v>
       </c>
       <c r="E97" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F97" t="s">
         <v>1</v>
       </c>
       <c r="G97" s="2">
-        <v>45995</v>
+        <v>46134</v>
       </c>
       <c r="H97" s="2">
-        <v>46167</v>
+        <v>46144</v>
       </c>
       <c r="I97" t="s">
         <v>4</v>
@@ -12110,10 +12170,10 @@
         <v>40</v>
       </c>
       <c r="L97" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="M97" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="N97" t="s">
         <v>9</v>
@@ -12125,10 +12185,10 @@
         <v>9</v>
       </c>
       <c r="Q97" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="R97" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="S97" t="s">
         <v>12</v>
@@ -12140,10 +12200,10 @@
         <v>45</v>
       </c>
       <c r="V97" s="3">
-        <v>250000.000</v>
+        <v>275740.000</v>
       </c>
       <c r="W97" s="3">
-        <v>139740.000</v>
+        <v>275740.000</v>
       </c>
       <c r="X97" s="3">
         <v>0.000</v>
@@ -12152,19 +12212,19 @@
         <v>15</v>
       </c>
       <c r="Z97" s="2">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="AA97" s="2">
-        <v>46205</v>
+        <v>46170</v>
       </c>
       <c r="AB97" s="2">
         <v>46174</v>
       </c>
       <c r="AC97" s="4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AD97" s="5">
-        <v>15.34</v>
+        <v>14.83</v>
       </c>
       <c r="AE97" t="s">
         <v>16</v>
@@ -12173,10 +12233,10 @@
         <v>1</v>
       </c>
       <c r="AG97" s="5">
-        <v>3835000.00</v>
+        <v>4089224.20</v>
       </c>
       <c r="AH97" s="5">
-        <v>2143611.60</v>
+        <v>4089224.20</v>
       </c>
       <c r="AI97" t="s">
         <v>17</v>
@@ -12193,10 +12253,10 @@
     </row>
     <row r="98" spans="1:38">
       <c r="A98" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B98" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C98" t="s">
         <v>2</v>
@@ -12205,16 +12265,16 @@
         <v>46167</v>
       </c>
       <c r="E98" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="F98" t="s">
         <v>1</v>
       </c>
       <c r="G98" s="2">
-        <v>46164</v>
+        <v>45995</v>
       </c>
       <c r="H98" s="2">
-        <v>46167</v>
+        <v>46106</v>
       </c>
       <c r="I98" t="s">
         <v>4</v>
@@ -12256,10 +12316,10 @@
         <v>45</v>
       </c>
       <c r="V98" s="3">
-        <v>300000.000</v>
+        <v>250000.000</v>
       </c>
       <c r="W98" s="3">
-        <v>229720.000</v>
+        <v>250000.000</v>
       </c>
       <c r="X98" s="3">
         <v>0.000</v>
@@ -12268,16 +12328,16 @@
         <v>15</v>
       </c>
       <c r="Z98" s="2">
-        <v>46192</v>
+        <v>46177</v>
       </c>
       <c r="AA98" s="2">
-        <v>46205</v>
+        <v>46181</v>
       </c>
       <c r="AB98" s="2">
         <v>46174</v>
       </c>
       <c r="AC98" s="4">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="AD98" s="5">
         <v>15.34</v>
@@ -12289,10 +12349,10 @@
         <v>1</v>
       </c>
       <c r="AG98" s="5">
-        <v>4602000.00</v>
+        <v>3835000.00</v>
       </c>
       <c r="AH98" s="5">
-        <v>3523904.80</v>
+        <v>3835000.00</v>
       </c>
       <c r="AI98" t="s">
         <v>17</v>
@@ -12309,10 +12369,10 @@
     </row>
     <row r="99" spans="1:38">
       <c r="A99" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B99" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="C99" t="s">
         <v>2</v>
@@ -12321,13 +12381,13 @@
         <v>46167</v>
       </c>
       <c r="E99" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="F99" t="s">
         <v>1</v>
       </c>
       <c r="G99" s="2">
-        <v>46164</v>
+        <v>45995</v>
       </c>
       <c r="H99" s="2">
         <v>46167</v>
@@ -12372,10 +12432,10 @@
         <v>45</v>
       </c>
       <c r="V99" s="3">
-        <v>190000.000</v>
+        <v>250000.000</v>
       </c>
       <c r="W99" s="3">
-        <v>190000.000</v>
+        <v>139740.000</v>
       </c>
       <c r="X99" s="3">
         <v>0.000</v>
@@ -12384,16 +12444,16 @@
         <v>15</v>
       </c>
       <c r="Z99" s="2">
-        <v>46175</v>
+        <v>46185</v>
       </c>
       <c r="AA99" s="2">
-        <v>46181</v>
+        <v>46205</v>
       </c>
       <c r="AB99" s="2">
         <v>46174</v>
       </c>
       <c r="AC99" s="4">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AD99" s="5">
         <v>15.34</v>
@@ -12405,10 +12465,10 @@
         <v>1</v>
       </c>
       <c r="AG99" s="5">
-        <v>2914600.00</v>
+        <v>3835000.00</v>
       </c>
       <c r="AH99" s="5">
-        <v>2914600.00</v>
+        <v>2143611.60</v>
       </c>
       <c r="AI99" t="s">
         <v>17</v>
@@ -12425,10 +12485,10 @@
     </row>
     <row r="100" spans="1:38">
       <c r="A100" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B100" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C100" t="s">
         <v>2</v>
@@ -12437,7 +12497,7 @@
         <v>46167</v>
       </c>
       <c r="E100" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="F100" t="s">
         <v>1</v>
@@ -12479,7 +12539,7 @@
         <v>44</v>
       </c>
       <c r="S100" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="T100" t="s">
         <v>13</v>
@@ -12488,10 +12548,10 @@
         <v>45</v>
       </c>
       <c r="V100" s="3">
-        <v>270000.000</v>
+        <v>300000.000</v>
       </c>
       <c r="W100" s="3">
-        <v>269820.000</v>
+        <v>229720.000</v>
       </c>
       <c r="X100" s="3">
         <v>0.000</v>
@@ -12500,7 +12560,7 @@
         <v>15</v>
       </c>
       <c r="Z100" s="2">
-        <v>46177</v>
+        <v>46192</v>
       </c>
       <c r="AA100" s="2">
         <v>46205</v>
@@ -12509,10 +12569,10 @@
         <v>46174</v>
       </c>
       <c r="AC100" s="4">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="AD100" s="5">
-        <v>15.39</v>
+        <v>15.34</v>
       </c>
       <c r="AE100" t="s">
         <v>16</v>
@@ -12521,10 +12581,10 @@
         <v>1</v>
       </c>
       <c r="AG100" s="5">
-        <v>4155300.00</v>
+        <v>4602000.00</v>
       </c>
       <c r="AH100" s="5">
-        <v>4152529.80</v>
+        <v>3523904.80</v>
       </c>
       <c r="AI100" t="s">
         <v>17</v>
@@ -12541,10 +12601,10 @@
     </row>
     <row r="101" spans="1:38">
       <c r="A101" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B101" t="s">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="C101" t="s">
         <v>2</v>
@@ -12553,16 +12613,16 @@
         <v>46167</v>
       </c>
       <c r="E101" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F101" t="s">
         <v>1</v>
       </c>
       <c r="G101" s="2">
-        <v>45890</v>
+        <v>46164</v>
       </c>
       <c r="H101" s="2">
-        <v>46120</v>
+        <v>46167</v>
       </c>
       <c r="I101" t="s">
         <v>4</v>
@@ -12595,7 +12655,7 @@
         <v>44</v>
       </c>
       <c r="S101" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="T101" t="s">
         <v>13</v>
@@ -12604,10 +12664,10 @@
         <v>45</v>
       </c>
       <c r="V101" s="3">
-        <v>225000.000</v>
+        <v>190000.000</v>
       </c>
       <c r="W101" s="3">
-        <v>224840.000</v>
+        <v>190000.000</v>
       </c>
       <c r="X101" s="3">
         <v>0.000</v>
@@ -12619,7 +12679,7 @@
         <v>46175</v>
       </c>
       <c r="AA101" s="2">
-        <v>46205</v>
+        <v>46181</v>
       </c>
       <c r="AB101" s="2">
         <v>46174</v>
@@ -12628,7 +12688,7 @@
         <v>1</v>
       </c>
       <c r="AD101" s="5">
-        <v>15.32</v>
+        <v>15.34</v>
       </c>
       <c r="AE101" t="s">
         <v>16</v>
@@ -12637,10 +12697,10 @@
         <v>1</v>
       </c>
       <c r="AG101" s="5">
-        <v>3447000.00</v>
+        <v>2914600.00</v>
       </c>
       <c r="AH101" s="5">
-        <v>3444548.80</v>
+        <v>2914600.00</v>
       </c>
       <c r="AI101" t="s">
         <v>17</v>
@@ -12657,10 +12717,10 @@
     </row>
     <row r="102" spans="1:38">
       <c r="A102" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B102" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C102" t="s">
         <v>2</v>
@@ -12669,7 +12729,7 @@
         <v>46167</v>
       </c>
       <c r="E102" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="F102" t="s">
         <v>1</v>
@@ -12711,7 +12771,7 @@
         <v>44</v>
       </c>
       <c r="S102" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="T102" t="s">
         <v>13</v>
@@ -12720,10 +12780,10 @@
         <v>45</v>
       </c>
       <c r="V102" s="3">
-        <v>23000.000</v>
+        <v>270000.000</v>
       </c>
       <c r="W102" s="3">
-        <v>23000.000</v>
+        <v>269820.000</v>
       </c>
       <c r="X102" s="3">
         <v>0.000</v>
@@ -12732,19 +12792,19 @@
         <v>15</v>
       </c>
       <c r="Z102" s="2">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="AA102" s="2">
-        <v>46169</v>
+        <v>46205</v>
       </c>
       <c r="AB102" s="2">
         <v>46174</v>
       </c>
       <c r="AC102" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD102" s="5">
-        <v>15.32</v>
+        <v>15.39</v>
       </c>
       <c r="AE102" t="s">
         <v>16</v>
@@ -12753,10 +12813,10 @@
         <v>1</v>
       </c>
       <c r="AG102" s="5">
-        <v>352360.00</v>
+        <v>4155300.00</v>
       </c>
       <c r="AH102" s="5">
-        <v>352360.00</v>
+        <v>4152529.80</v>
       </c>
       <c r="AI102" t="s">
         <v>17</v>
@@ -12773,7 +12833,7 @@
     </row>
     <row r="103" spans="1:38">
       <c r="A103" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B103" t="s">
         <v>1</v>
@@ -12785,7 +12845,7 @@
         <v>46167</v>
       </c>
       <c r="E103" t="s">
-        <v>128</v>
+        <v>196</v>
       </c>
       <c r="F103" t="s">
         <v>1</v>
@@ -12806,10 +12866,10 @@
         <v>40</v>
       </c>
       <c r="L103" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="M103" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="N103" t="s">
         <v>9</v>
@@ -12827,7 +12887,7 @@
         <v>44</v>
       </c>
       <c r="S103" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="T103" t="s">
         <v>13</v>
@@ -12836,10 +12896,10 @@
         <v>45</v>
       </c>
       <c r="V103" s="3">
-        <v>30000.000</v>
+        <v>225000.000</v>
       </c>
       <c r="W103" s="3">
-        <v>29980.000</v>
+        <v>224840.000</v>
       </c>
       <c r="X103" s="3">
         <v>0.000</v>
@@ -12860,7 +12920,7 @@
         <v>1</v>
       </c>
       <c r="AD103" s="5">
-        <v>15.40</v>
+        <v>15.32</v>
       </c>
       <c r="AE103" t="s">
         <v>16</v>
@@ -12869,10 +12929,10 @@
         <v>1</v>
       </c>
       <c r="AG103" s="5">
-        <v>462000.00</v>
+        <v>3447000.00</v>
       </c>
       <c r="AH103" s="5">
-        <v>461692.00</v>
+        <v>3444548.80</v>
       </c>
       <c r="AI103" t="s">
         <v>17</v>
@@ -12889,7 +12949,7 @@
     </row>
     <row r="104" spans="1:38">
       <c r="A104" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B104" t="s">
         <v>19</v>
@@ -12901,7 +12961,7 @@
         <v>46167</v>
       </c>
       <c r="E104" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="F104" t="s">
         <v>1</v>
@@ -12922,10 +12982,10 @@
         <v>40</v>
       </c>
       <c r="L104" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="M104" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="N104" t="s">
         <v>9</v>
@@ -12943,7 +13003,7 @@
         <v>44</v>
       </c>
       <c r="S104" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="T104" t="s">
         <v>13</v>
@@ -12952,10 +13012,10 @@
         <v>45</v>
       </c>
       <c r="V104" s="3">
-        <v>300000.000</v>
+        <v>23000.000</v>
       </c>
       <c r="W104" s="3">
-        <v>239840.000</v>
+        <v>23000.000</v>
       </c>
       <c r="X104" s="3">
         <v>0.000</v>
@@ -12964,19 +13024,19 @@
         <v>15</v>
       </c>
       <c r="Z104" s="2">
-        <v>46177</v>
+        <v>46175</v>
       </c>
       <c r="AA104" s="2">
-        <v>46205</v>
+        <v>46169</v>
       </c>
       <c r="AB104" s="2">
         <v>46174</v>
       </c>
       <c r="AC104" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD104" s="5">
-        <v>15.40</v>
+        <v>15.32</v>
       </c>
       <c r="AE104" t="s">
         <v>16</v>
@@ -12985,10 +13045,10 @@
         <v>1</v>
       </c>
       <c r="AG104" s="5">
-        <v>4620000.00</v>
+        <v>352360.00</v>
       </c>
       <c r="AH104" s="5">
-        <v>3693536.00</v>
+        <v>352360.00</v>
       </c>
       <c r="AI104" t="s">
         <v>17</v>
@@ -13005,7 +13065,7 @@
     </row>
     <row r="105" spans="1:38">
       <c r="A105" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B105" t="s">
         <v>1</v>
@@ -13017,16 +13077,16 @@
         <v>46167</v>
       </c>
       <c r="E105" t="s">
-        <v>177</v>
+        <v>128</v>
       </c>
       <c r="F105" t="s">
         <v>1</v>
       </c>
       <c r="G105" s="2">
-        <v>46164</v>
+        <v>45890</v>
       </c>
       <c r="H105" s="2">
-        <v>46167</v>
+        <v>46120</v>
       </c>
       <c r="I105" t="s">
         <v>4</v>
@@ -13059,7 +13119,7 @@
         <v>44</v>
       </c>
       <c r="S105" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="T105" t="s">
         <v>13</v>
@@ -13068,10 +13128,10 @@
         <v>45</v>
       </c>
       <c r="V105" s="3">
-        <v>60000.000</v>
+        <v>30000.000</v>
       </c>
       <c r="W105" s="3">
-        <v>59960.000</v>
+        <v>29980.000</v>
       </c>
       <c r="X105" s="3">
         <v>0.000</v>
@@ -13080,19 +13140,19 @@
         <v>15</v>
       </c>
       <c r="Z105" s="2">
-        <v>46182</v>
+        <v>46175</v>
       </c>
       <c r="AA105" s="2">
-        <v>46200</v>
+        <v>46205</v>
       </c>
       <c r="AB105" s="2">
         <v>46174</v>
       </c>
       <c r="AC105" s="4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AD105" s="5">
-        <v>16.21</v>
+        <v>15.40</v>
       </c>
       <c r="AE105" t="s">
         <v>16</v>
@@ -13101,10 +13161,10 @@
         <v>1</v>
       </c>
       <c r="AG105" s="5">
-        <v>972600.00</v>
+        <v>462000.00</v>
       </c>
       <c r="AH105" s="5">
-        <v>971951.60</v>
+        <v>461692.00</v>
       </c>
       <c r="AI105" t="s">
         <v>17</v>
@@ -13121,43 +13181,43 @@
     </row>
     <row r="106" spans="1:38">
       <c r="A106" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B106" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C106" t="s">
         <v>2</v>
       </c>
       <c r="D106" s="2">
-        <v>46188</v>
+        <v>46167</v>
       </c>
       <c r="E106" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F106" t="s">
         <v>1</v>
       </c>
       <c r="G106" s="2">
-        <v>46188</v>
+        <v>46164</v>
       </c>
       <c r="H106" s="2">
-        <v>46188</v>
+        <v>46167</v>
       </c>
       <c r="I106" t="s">
         <v>4</v>
       </c>
       <c r="J106" t="s">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="K106" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="L106" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="M106" t="s">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="N106" t="s">
         <v>9</v>
@@ -13169,25 +13229,25 @@
         <v>9</v>
       </c>
       <c r="Q106" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="R106" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="S106" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T106" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="U106" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="V106" s="3">
-        <v>450.000</v>
+        <v>300000.000</v>
       </c>
       <c r="W106" s="3">
-        <v>450.000</v>
+        <v>239840.000</v>
       </c>
       <c r="X106" s="3">
         <v>0.000</v>
@@ -13196,19 +13256,19 @@
         <v>15</v>
       </c>
       <c r="Z106" s="2">
-        <v>46197</v>
+        <v>46177</v>
       </c>
       <c r="AA106" s="2">
-        <v>46190</v>
+        <v>46205</v>
       </c>
       <c r="AB106" s="2">
-        <v>46224</v>
+        <v>46174</v>
       </c>
       <c r="AC106" s="4">
-        <v>-27</v>
+        <v>3</v>
       </c>
       <c r="AD106" s="5">
-        <v>6.66</v>
+        <v>15.40</v>
       </c>
       <c r="AE106" t="s">
         <v>16</v>
@@ -13217,10 +13277,10 @@
         <v>1</v>
       </c>
       <c r="AG106" s="5">
-        <v>2997.00</v>
+        <v>4620000.00</v>
       </c>
       <c r="AH106" s="5">
-        <v>2997.00</v>
+        <v>3693536.00</v>
       </c>
       <c r="AI106" t="s">
         <v>17</v>
@@ -13237,7 +13297,7 @@
     </row>
     <row r="107" spans="1:38">
       <c r="A107" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B107" t="s">
         <v>1</v>
@@ -13246,34 +13306,34 @@
         <v>2</v>
       </c>
       <c r="D107" s="2">
-        <v>46192</v>
+        <v>46167</v>
       </c>
       <c r="E107" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F107" t="s">
         <v>1</v>
       </c>
       <c r="G107" s="2">
-        <v>46120</v>
+        <v>46164</v>
       </c>
       <c r="H107" s="2">
-        <v>46122</v>
+        <v>46167</v>
       </c>
       <c r="I107" t="s">
         <v>4</v>
       </c>
       <c r="J107" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="K107" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L107" t="s">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="M107" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="N107" t="s">
         <v>9</v>
@@ -13285,25 +13345,25 @@
         <v>9</v>
       </c>
       <c r="Q107" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="R107" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="S107" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="T107" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="U107" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="V107" s="3">
         <v>60000.000</v>
       </c>
       <c r="W107" s="3">
-        <v>57330.000</v>
+        <v>59960.000</v>
       </c>
       <c r="X107" s="3">
         <v>0.000</v>
@@ -13312,19 +13372,19 @@
         <v>15</v>
       </c>
       <c r="Z107" s="2">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="AA107" s="2">
-        <v>46196</v>
+        <v>46200</v>
       </c>
       <c r="AB107" s="2">
-        <v>46193</v>
+        <v>46174</v>
       </c>
       <c r="AC107" s="4">
-        <v>-9</v>
+        <v>8</v>
       </c>
       <c r="AD107" s="5">
-        <v>5.07</v>
+        <v>16.21</v>
       </c>
       <c r="AE107" t="s">
         <v>16</v>
@@ -13333,10 +13393,10 @@
         <v>1</v>
       </c>
       <c r="AG107" s="5">
-        <v>304200.00</v>
+        <v>972600.00</v>
       </c>
       <c r="AH107" s="5">
-        <v>290663.10</v>
+        <v>971951.60</v>
       </c>
       <c r="AI107" t="s">
         <v>17</v>
@@ -13353,43 +13413,43 @@
     </row>
     <row r="108" spans="1:38">
       <c r="A108" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B108" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C108" t="s">
         <v>2</v>
       </c>
       <c r="D108" s="2">
-        <v>46193</v>
+        <v>46188</v>
       </c>
       <c r="E108" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F108" t="s">
         <v>1</v>
       </c>
       <c r="G108" s="2">
-        <v>46105</v>
+        <v>46188</v>
       </c>
       <c r="H108" s="2">
-        <v>46105</v>
+        <v>46188</v>
       </c>
       <c r="I108" t="s">
         <v>4</v>
       </c>
       <c r="J108" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K108" t="s">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="L108" t="s">
-        <v>7</v>
+        <v>102</v>
       </c>
       <c r="M108" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="N108" t="s">
         <v>9</v>
@@ -13407,19 +13467,19 @@
         <v>11</v>
       </c>
       <c r="S108" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="T108" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="U108" t="s">
         <v>14</v>
       </c>
       <c r="V108" s="3">
-        <v>20000.000</v>
+        <v>450.000</v>
       </c>
       <c r="W108" s="3">
-        <v>18670.000</v>
+        <v>450.000</v>
       </c>
       <c r="X108" s="3">
         <v>0.000</v>
@@ -13428,19 +13488,19 @@
         <v>15</v>
       </c>
       <c r="Z108" s="2">
-        <v>46202</v>
+        <v>46197</v>
       </c>
       <c r="AA108" s="2">
-        <v>46196</v>
+        <v>46190</v>
       </c>
       <c r="AB108" s="2">
-        <v>46196</v>
+        <v>46224</v>
       </c>
       <c r="AC108" s="4">
-        <v>6</v>
+        <v>-27</v>
       </c>
       <c r="AD108" s="5">
-        <v>6.06</v>
+        <v>6.66</v>
       </c>
       <c r="AE108" t="s">
         <v>16</v>
@@ -13449,10 +13509,10 @@
         <v>1</v>
       </c>
       <c r="AG108" s="5">
-        <v>121200.00</v>
+        <v>2997.00</v>
       </c>
       <c r="AH108" s="5">
-        <v>113140.20</v>
+        <v>2997.00</v>
       </c>
       <c r="AI108" t="s">
         <v>17</v>
@@ -13469,7 +13529,7 @@
     </row>
     <row r="109" spans="1:38">
       <c r="A109" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B109" t="s">
         <v>1</v>
@@ -13478,34 +13538,34 @@
         <v>2</v>
       </c>
       <c r="D109" s="2">
-        <v>46198</v>
+        <v>46192</v>
       </c>
       <c r="E109" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F109" t="s">
         <v>1</v>
       </c>
       <c r="G109" s="2">
-        <v>46134</v>
+        <v>46120</v>
       </c>
       <c r="H109" s="2">
-        <v>46198</v>
+        <v>46122</v>
       </c>
       <c r="I109" t="s">
         <v>4</v>
       </c>
       <c r="J109" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="K109" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="L109" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="M109" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="N109" t="s">
         <v>9</v>
@@ -13517,46 +13577,46 @@
         <v>9</v>
       </c>
       <c r="Q109" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="R109" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="S109" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T109" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="U109" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="V109" s="3">
-        <v>275000.000</v>
+        <v>60000.000</v>
       </c>
       <c r="W109" s="3">
-        <v>143830.000</v>
+        <v>57330.000</v>
       </c>
       <c r="X109" s="3">
-        <v>131170.000</v>
+        <v>0.000</v>
       </c>
       <c r="Y109" t="s">
         <v>15</v>
       </c>
       <c r="Z109" s="2">
-        <v>46204</v>
+        <v>46184</v>
       </c>
       <c r="AA109" s="2">
-        <v>46202</v>
+        <v>46196</v>
       </c>
       <c r="AB109" s="2">
-        <v>46204</v>
+        <v>46193</v>
       </c>
       <c r="AC109" s="4">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="AD109" s="5">
-        <v>14.82</v>
+        <v>5.07</v>
       </c>
       <c r="AE109" t="s">
         <v>16</v>
@@ -13565,13 +13625,13 @@
         <v>1</v>
       </c>
       <c r="AG109" s="5">
-        <v>4075500.00</v>
+        <v>304200.00</v>
       </c>
       <c r="AH109" s="5">
-        <v>2131560.60</v>
+        <v>290663.10</v>
       </c>
       <c r="AI109" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AJ109" t="s">
         <v>9</v>
@@ -13585,7 +13645,7 @@
     </row>
     <row r="110" spans="1:38">
       <c r="A110" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B110" t="s">
         <v>1</v>
@@ -13594,34 +13654,34 @@
         <v>2</v>
       </c>
       <c r="D110" s="2">
-        <v>46199</v>
+        <v>46193</v>
       </c>
       <c r="E110" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F110" t="s">
         <v>1</v>
       </c>
       <c r="G110" s="2">
-        <v>46134</v>
+        <v>46105</v>
       </c>
       <c r="H110" s="2">
-        <v>46198</v>
+        <v>46105</v>
       </c>
       <c r="I110" t="s">
         <v>4</v>
       </c>
       <c r="J110" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="K110" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="L110" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="M110" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="N110" t="s">
         <v>9</v>
@@ -13633,25 +13693,25 @@
         <v>9</v>
       </c>
       <c r="Q110" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="R110" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="S110" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="T110" t="s">
         <v>13</v>
       </c>
       <c r="U110" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="V110" s="3">
-        <v>35000.000</v>
+        <v>20000.000</v>
       </c>
       <c r="W110" s="3">
-        <v>35000.000</v>
+        <v>18670.000</v>
       </c>
       <c r="X110" s="3">
         <v>0.000</v>
@@ -13660,19 +13720,19 @@
         <v>15</v>
       </c>
       <c r="Z110" s="2">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="AA110" s="2">
-        <v>46202</v>
+        <v>46196</v>
       </c>
       <c r="AB110" s="2">
-        <v>46200</v>
+        <v>46196</v>
       </c>
       <c r="AC110" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD110" s="5">
-        <v>14.83</v>
+        <v>6.06</v>
       </c>
       <c r="AE110" t="s">
         <v>16</v>
@@ -13681,10 +13741,10 @@
         <v>1</v>
       </c>
       <c r="AG110" s="5">
-        <v>519050.00</v>
+        <v>121200.00</v>
       </c>
       <c r="AH110" s="5">
-        <v>519050.00</v>
+        <v>113140.20</v>
       </c>
       <c r="AI110" t="s">
         <v>17</v>
@@ -13701,28 +13761,28 @@
     </row>
     <row r="111" spans="1:38">
       <c r="A111" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B111" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C111" t="s">
         <v>2</v>
       </c>
       <c r="D111" s="2">
-        <v>46199</v>
+        <v>46197</v>
       </c>
       <c r="E111" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="F111" t="s">
         <v>1</v>
       </c>
       <c r="G111" s="2">
-        <v>46134</v>
+        <v>46122</v>
       </c>
       <c r="H111" s="2">
-        <v>46199</v>
+        <v>46197</v>
       </c>
       <c r="I111" t="s">
         <v>4</v>
@@ -13749,10 +13809,10 @@
         <v>9</v>
       </c>
       <c r="Q111" t="s">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="R111" t="s">
-        <v>64</v>
+        <v>134</v>
       </c>
       <c r="S111" t="s">
         <v>12</v>
@@ -13761,34 +13821,34 @@
         <v>13</v>
       </c>
       <c r="U111" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="V111" s="3">
-        <v>40000.000</v>
+        <v>18900.000</v>
       </c>
       <c r="W111" s="3">
-        <v>5080.000</v>
+        <v>18900.000</v>
       </c>
       <c r="X111" s="3">
-        <v>34920.000</v>
+        <v>0.000</v>
       </c>
       <c r="Y111" t="s">
         <v>15</v>
       </c>
       <c r="Z111" s="2">
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="AA111" s="2">
         <v>46202</v>
       </c>
       <c r="AB111" s="2">
-        <v>46200</v>
+        <v>46204</v>
       </c>
       <c r="AC111" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD111" s="5">
-        <v>14.83</v>
+        <v>47.95</v>
       </c>
       <c r="AE111" t="s">
         <v>16</v>
@@ -13797,13 +13857,13 @@
         <v>1</v>
       </c>
       <c r="AG111" s="5">
-        <v>593200.00</v>
+        <v>906255.00</v>
       </c>
       <c r="AH111" s="5">
-        <v>75336.40</v>
+        <v>906255.00</v>
       </c>
       <c r="AI111" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AJ111" t="s">
         <v>9</v>
@@ -13817,7 +13877,7 @@
     </row>
     <row r="112" spans="1:38">
       <c r="A112" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B112" t="s">
         <v>1</v>
@@ -13826,19 +13886,19 @@
         <v>2</v>
       </c>
       <c r="D112" s="2">
-        <v>46199</v>
+        <v>46198</v>
       </c>
       <c r="E112" t="s">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="F112" t="s">
         <v>1</v>
       </c>
       <c r="G112" s="2">
-        <v>45995</v>
+        <v>46134</v>
       </c>
       <c r="H112" s="2">
-        <v>46135</v>
+        <v>46198</v>
       </c>
       <c r="I112" t="s">
         <v>4</v>
@@ -13850,10 +13910,10 @@
         <v>40</v>
       </c>
       <c r="L112" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="M112" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="N112" t="s">
         <v>9</v>
@@ -13865,10 +13925,10 @@
         <v>9</v>
       </c>
       <c r="Q112" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="R112" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="S112" t="s">
         <v>12</v>
@@ -13880,13 +13940,13 @@
         <v>45</v>
       </c>
       <c r="V112" s="3">
-        <v>100000.000</v>
+        <v>275000.000</v>
       </c>
       <c r="W112" s="3">
-        <v>100000.000</v>
+        <v>143830.000</v>
       </c>
       <c r="X112" s="3">
-        <v>0.000</v>
+        <v>131170.000</v>
       </c>
       <c r="Y112" t="s">
         <v>15</v>
@@ -13895,7 +13955,7 @@
         <v>46204</v>
       </c>
       <c r="AA112" s="2">
-        <v>46204</v>
+        <v>46202</v>
       </c>
       <c r="AB112" s="2">
         <v>46204</v>
@@ -13904,7 +13964,7 @@
         <v>0</v>
       </c>
       <c r="AD112" s="5">
-        <v>15.31</v>
+        <v>14.82</v>
       </c>
       <c r="AE112" t="s">
         <v>16</v>
@@ -13913,13 +13973,13 @@
         <v>1</v>
       </c>
       <c r="AG112" s="5">
-        <v>1531000.00</v>
+        <v>4075500.00</v>
       </c>
       <c r="AH112" s="5">
-        <v>1531000.00</v>
+        <v>2131560.60</v>
       </c>
       <c r="AI112" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AJ112" t="s">
         <v>9</v>
@@ -13933,10 +13993,10 @@
     </row>
     <row r="113" spans="1:38">
       <c r="A113" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B113" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C113" t="s">
         <v>2</v>
@@ -13945,16 +14005,16 @@
         <v>46199</v>
       </c>
       <c r="E113" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="F113" t="s">
         <v>1</v>
       </c>
       <c r="G113" s="2">
-        <v>46164</v>
+        <v>46134</v>
       </c>
       <c r="H113" s="2">
-        <v>46167</v>
+        <v>46198</v>
       </c>
       <c r="I113" t="s">
         <v>4</v>
@@ -13966,10 +14026,10 @@
         <v>40</v>
       </c>
       <c r="L113" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="M113" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="N113" t="s">
         <v>9</v>
@@ -13981,10 +14041,10 @@
         <v>9</v>
       </c>
       <c r="Q113" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="R113" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="S113" t="s">
         <v>12</v>
@@ -13996,10 +14056,10 @@
         <v>45</v>
       </c>
       <c r="V113" s="3">
-        <v>110000.000</v>
+        <v>35000.000</v>
       </c>
       <c r="W113" s="3">
-        <v>110000.000</v>
+        <v>35000.000</v>
       </c>
       <c r="X113" s="3">
         <v>0.000</v>
@@ -14008,19 +14068,19 @@
         <v>15</v>
       </c>
       <c r="Z113" s="2">
-        <v>46207</v>
+        <v>46200</v>
       </c>
       <c r="AA113" s="2">
-        <v>46204</v>
+        <v>46202</v>
       </c>
       <c r="AB113" s="2">
-        <v>46204</v>
+        <v>46200</v>
       </c>
       <c r="AC113" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD113" s="5">
-        <v>15.31</v>
+        <v>14.83</v>
       </c>
       <c r="AE113" t="s">
         <v>16</v>
@@ -14029,10 +14089,10 @@
         <v>1</v>
       </c>
       <c r="AG113" s="5">
-        <v>1684100.00</v>
+        <v>519050.00</v>
       </c>
       <c r="AH113" s="5">
-        <v>1684100.00</v>
+        <v>519050.00</v>
       </c>
       <c r="AI113" t="s">
         <v>17</v>
@@ -14049,10 +14109,10 @@
     </row>
     <row r="114" spans="1:38">
       <c r="A114" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B114" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C114" t="s">
         <v>2</v>
@@ -14061,13 +14121,13 @@
         <v>46199</v>
       </c>
       <c r="E114" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="F114" t="s">
         <v>1</v>
       </c>
       <c r="G114" s="2">
-        <v>46164</v>
+        <v>46134</v>
       </c>
       <c r="H114" s="2">
         <v>46199</v>
@@ -14082,10 +14142,10 @@
         <v>40</v>
       </c>
       <c r="L114" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="M114" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="N114" t="s">
         <v>9</v>
@@ -14097,10 +14157,10 @@
         <v>9</v>
       </c>
       <c r="Q114" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="R114" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="S114" t="s">
         <v>12</v>
@@ -14112,31 +14172,31 @@
         <v>45</v>
       </c>
       <c r="V114" s="3">
-        <v>300000.000</v>
+        <v>40000.000</v>
       </c>
       <c r="W114" s="3">
-        <v>179740.000</v>
+        <v>5080.000</v>
       </c>
       <c r="X114" s="3">
-        <v>120260.000</v>
+        <v>34920.000</v>
       </c>
       <c r="Y114" t="s">
         <v>15</v>
       </c>
       <c r="Z114" s="2">
-        <v>46211</v>
+        <v>46202</v>
       </c>
       <c r="AA114" s="2">
-        <v>46204</v>
+        <v>46202</v>
       </c>
       <c r="AB114" s="2">
-        <v>46204</v>
+        <v>46200</v>
       </c>
       <c r="AC114" s="4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AD114" s="5">
-        <v>15.31</v>
+        <v>14.83</v>
       </c>
       <c r="AE114" t="s">
         <v>16</v>
@@ -14145,10 +14205,10 @@
         <v>1</v>
       </c>
       <c r="AG114" s="5">
-        <v>4593000.00</v>
+        <v>593200.00</v>
       </c>
       <c r="AH114" s="5">
-        <v>2751819.40</v>
+        <v>75336.40</v>
       </c>
       <c r="AI114" t="s">
         <v>9</v>
@@ -14165,10 +14225,10 @@
     </row>
     <row r="115" spans="1:38">
       <c r="A115" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="B115" t="s">
-        <v>86</v>
+        <v>1</v>
       </c>
       <c r="C115" t="s">
         <v>2</v>
@@ -14177,16 +14237,16 @@
         <v>46199</v>
       </c>
       <c r="E115" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="F115" t="s">
         <v>1</v>
       </c>
       <c r="G115" s="2">
-        <v>46164</v>
+        <v>46122</v>
       </c>
       <c r="H115" s="2">
-        <v>46199</v>
+        <v>46197</v>
       </c>
       <c r="I115" t="s">
         <v>4</v>
@@ -14198,10 +14258,10 @@
         <v>40</v>
       </c>
       <c r="L115" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="M115" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="N115" t="s">
         <v>9</v>
@@ -14213,10 +14273,10 @@
         <v>9</v>
       </c>
       <c r="Q115" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="R115" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="S115" t="s">
         <v>12</v>
@@ -14225,32 +14285,34 @@
         <v>13</v>
       </c>
       <c r="U115" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="V115" s="3">
-        <v>300000.000</v>
+        <v>1000.000</v>
       </c>
       <c r="W115" s="3">
+        <v>1000.000</v>
+      </c>
+      <c r="X115" s="3">
         <v>0.000</v>
-      </c>
-      <c r="X115" s="3">
-        <v>300000.000</v>
       </c>
       <c r="Y115" t="s">
         <v>15</v>
       </c>
-      <c r="Z115" s="2"/>
+      <c r="Z115" s="2">
+        <v>46213</v>
+      </c>
       <c r="AA115" s="2">
-        <v>46204</v>
+        <v>46203</v>
       </c>
       <c r="AB115" s="2">
         <v>46204</v>
       </c>
       <c r="AC115" s="4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD115" s="5">
-        <v>15.31</v>
+        <v>47.95</v>
       </c>
       <c r="AE115" t="s">
         <v>16</v>
@@ -14259,13 +14321,13 @@
         <v>1</v>
       </c>
       <c r="AG115" s="5">
-        <v>4593000.00</v>
+        <v>47950.00</v>
       </c>
       <c r="AH115" s="5">
-        <v>0.00</v>
+        <v>47950.00</v>
       </c>
       <c r="AI115" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AJ115" t="s">
         <v>9</v>
@@ -14279,10 +14341,10 @@
     </row>
     <row r="116" spans="1:38">
       <c r="A116" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="B116" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="C116" t="s">
         <v>2</v>
@@ -14291,13 +14353,13 @@
         <v>46199</v>
       </c>
       <c r="E116" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="F116" t="s">
         <v>1</v>
       </c>
       <c r="G116" s="2">
-        <v>46164</v>
+        <v>46197</v>
       </c>
       <c r="H116" s="2">
         <v>46199</v>
@@ -14312,10 +14374,10 @@
         <v>40</v>
       </c>
       <c r="L116" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="M116" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="N116" t="s">
         <v>9</v>
@@ -14327,10 +14389,10 @@
         <v>9</v>
       </c>
       <c r="Q116" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="R116" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="S116" t="s">
         <v>12</v>
@@ -14339,32 +14401,34 @@
         <v>13</v>
       </c>
       <c r="U116" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="V116" s="3">
-        <v>90000.000</v>
+        <v>100000.000</v>
       </c>
       <c r="W116" s="3">
-        <v>0.000</v>
+        <v>12500.000</v>
       </c>
       <c r="X116" s="3">
-        <v>90000.000</v>
+        <v>87500.000</v>
       </c>
       <c r="Y116" t="s">
         <v>15</v>
       </c>
-      <c r="Z116" s="2"/>
+      <c r="Z116" s="2">
+        <v>46213</v>
+      </c>
       <c r="AA116" s="2">
-        <v>46204</v>
+        <v>46203</v>
       </c>
       <c r="AB116" s="2">
         <v>46204</v>
       </c>
       <c r="AC116" s="4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD116" s="5">
-        <v>15.31</v>
+        <v>47.95</v>
       </c>
       <c r="AE116" t="s">
         <v>16</v>
@@ -14373,10 +14437,10 @@
         <v>1</v>
       </c>
       <c r="AG116" s="5">
-        <v>1377900.00</v>
+        <v>4795000.00</v>
       </c>
       <c r="AH116" s="5">
-        <v>0.00</v>
+        <v>599375.00</v>
       </c>
       <c r="AI116" t="s">
         <v>9</v>
@@ -14393,10 +14457,10 @@
     </row>
     <row r="117" spans="1:38">
       <c r="A117" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B117" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C117" t="s">
         <v>2</v>
@@ -14405,16 +14469,16 @@
         <v>46199</v>
       </c>
       <c r="E117" t="s">
-        <v>128</v>
+        <v>215</v>
       </c>
       <c r="F117" t="s">
         <v>1</v>
       </c>
       <c r="G117" s="2">
-        <v>45890</v>
+        <v>46197</v>
       </c>
       <c r="H117" s="2">
-        <v>46120</v>
+        <v>46199</v>
       </c>
       <c r="I117" t="s">
         <v>4</v>
@@ -14426,10 +14490,10 @@
         <v>40</v>
       </c>
       <c r="L117" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="M117" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="N117" t="s">
         <v>9</v>
@@ -14441,28 +14505,28 @@
         <v>9</v>
       </c>
       <c r="Q117" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="R117" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="S117" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T117" t="s">
         <v>13</v>
       </c>
       <c r="U117" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="V117" s="3">
-        <v>22500.000</v>
+        <v>100000.000</v>
       </c>
       <c r="W117" s="3">
         <v>0.000</v>
       </c>
       <c r="X117" s="3">
-        <v>22500.000</v>
+        <v>100000.000</v>
       </c>
       <c r="Y117" t="s">
         <v>15</v>
@@ -14478,7 +14542,7 @@
         <v>0</v>
       </c>
       <c r="AD117" s="5">
-        <v>15.38</v>
+        <v>47.95</v>
       </c>
       <c r="AE117" t="s">
         <v>16</v>
@@ -14487,7 +14551,7 @@
         <v>1</v>
       </c>
       <c r="AG117" s="5">
-        <v>346050.00</v>
+        <v>4795000.00</v>
       </c>
       <c r="AH117" s="5">
         <v>0.00</v>
@@ -14507,10 +14571,10 @@
     </row>
     <row r="118" spans="1:38">
       <c r="A118" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B118" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="C118" t="s">
         <v>2</v>
@@ -14519,16 +14583,16 @@
         <v>46199</v>
       </c>
       <c r="E118" t="s">
-        <v>139</v>
+        <v>216</v>
       </c>
       <c r="F118" t="s">
         <v>1</v>
       </c>
       <c r="G118" s="2">
-        <v>45997</v>
+        <v>46197</v>
       </c>
       <c r="H118" s="2">
-        <v>46135</v>
+        <v>46199</v>
       </c>
       <c r="I118" t="s">
         <v>4</v>
@@ -14540,10 +14604,10 @@
         <v>40</v>
       </c>
       <c r="L118" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="M118" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="N118" t="s">
         <v>9</v>
@@ -14555,35 +14619,33 @@
         <v>9</v>
       </c>
       <c r="Q118" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="R118" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="S118" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T118" t="s">
         <v>13</v>
       </c>
       <c r="U118" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="V118" s="3">
-        <v>40000.000</v>
+        <v>100000.000</v>
       </c>
       <c r="W118" s="3">
-        <v>29980.000</v>
+        <v>0.000</v>
       </c>
       <c r="X118" s="3">
-        <v>10020.000</v>
+        <v>100000.000</v>
       </c>
       <c r="Y118" t="s">
         <v>15</v>
       </c>
-      <c r="Z118" s="2">
-        <v>46206</v>
-      </c>
+      <c r="Z118" s="2"/>
       <c r="AA118" s="2">
         <v>46203</v>
       </c>
@@ -14591,10 +14653,10 @@
         <v>46204</v>
       </c>
       <c r="AC118" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD118" s="5">
-        <v>15.38</v>
+        <v>47.95</v>
       </c>
       <c r="AE118" t="s">
         <v>16</v>
@@ -14603,10 +14665,10 @@
         <v>1</v>
       </c>
       <c r="AG118" s="5">
-        <v>615200.00</v>
+        <v>4795000.00</v>
       </c>
       <c r="AH118" s="5">
-        <v>461092.40</v>
+        <v>0.00</v>
       </c>
       <c r="AI118" t="s">
         <v>9</v>
@@ -14623,10 +14685,10 @@
     </row>
     <row r="119" spans="1:38">
       <c r="A119" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B119" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="C119" t="s">
         <v>2</v>
@@ -14635,13 +14697,13 @@
         <v>46199</v>
       </c>
       <c r="E119" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="F119" t="s">
         <v>1</v>
       </c>
       <c r="G119" s="2">
-        <v>46164</v>
+        <v>46197</v>
       </c>
       <c r="H119" s="2">
         <v>46199</v>
@@ -14656,10 +14718,10 @@
         <v>40</v>
       </c>
       <c r="L119" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="M119" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="N119" t="s">
         <v>9</v>
@@ -14671,35 +14733,33 @@
         <v>9</v>
       </c>
       <c r="Q119" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="R119" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="S119" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T119" t="s">
         <v>13</v>
       </c>
       <c r="U119" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="V119" s="3">
-        <v>240000.000</v>
+        <v>50000.000</v>
       </c>
       <c r="W119" s="3">
-        <v>29980.000</v>
+        <v>0.000</v>
       </c>
       <c r="X119" s="3">
-        <v>210020.000</v>
+        <v>50000.000</v>
       </c>
       <c r="Y119" t="s">
         <v>15</v>
       </c>
-      <c r="Z119" s="2">
-        <v>46212</v>
-      </c>
+      <c r="Z119" s="2"/>
       <c r="AA119" s="2">
         <v>46203</v>
       </c>
@@ -14707,10 +14767,10 @@
         <v>46204</v>
       </c>
       <c r="AC119" s="4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD119" s="5">
-        <v>15.38</v>
+        <v>47.95</v>
       </c>
       <c r="AE119" t="s">
         <v>16</v>
@@ -14719,10 +14779,10 @@
         <v>1</v>
       </c>
       <c r="AG119" s="5">
-        <v>3691200.00</v>
+        <v>2397500.00</v>
       </c>
       <c r="AH119" s="5">
-        <v>461092.40</v>
+        <v>0.00</v>
       </c>
       <c r="AI119" t="s">
         <v>9</v>
@@ -14739,7 +14799,7 @@
     </row>
     <row r="120" spans="1:38">
       <c r="A120" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="B120" t="s">
         <v>1</v>
@@ -14751,16 +14811,16 @@
         <v>46199</v>
       </c>
       <c r="E120" t="s">
-        <v>126</v>
+        <v>219</v>
       </c>
       <c r="F120" t="s">
         <v>1</v>
       </c>
       <c r="G120" s="2">
-        <v>45890</v>
+        <v>46197</v>
       </c>
       <c r="H120" s="2">
-        <v>46120</v>
+        <v>46199</v>
       </c>
       <c r="I120" t="s">
         <v>4</v>
@@ -14772,10 +14832,10 @@
         <v>40</v>
       </c>
       <c r="L120" t="s">
-        <v>41</v>
+        <v>131</v>
       </c>
       <c r="M120" t="s">
-        <v>42</v>
+        <v>132</v>
       </c>
       <c r="N120" t="s">
         <v>9</v>
@@ -14787,10 +14847,10 @@
         <v>9</v>
       </c>
       <c r="Q120" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="R120" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="S120" t="s">
         <v>28</v>
@@ -14799,34 +14859,34 @@
         <v>13</v>
       </c>
       <c r="U120" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="V120" s="3">
-        <v>215000.000</v>
+        <v>99400.000</v>
       </c>
       <c r="W120" s="3">
-        <v>89940.000</v>
+        <v>8400.000</v>
       </c>
       <c r="X120" s="3">
-        <v>125060.000</v>
+        <v>91000.000</v>
       </c>
       <c r="Y120" t="s">
         <v>15</v>
       </c>
       <c r="Z120" s="2">
-        <v>46207</v>
+        <v>46213</v>
       </c>
       <c r="AA120" s="2">
-        <v>46202</v>
+        <v>46211</v>
       </c>
       <c r="AB120" s="2">
         <v>46204</v>
       </c>
       <c r="AC120" s="4">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AD120" s="5">
-        <v>15.36</v>
+        <v>47.90</v>
       </c>
       <c r="AE120" t="s">
         <v>16</v>
@@ -14835,10 +14895,10 @@
         <v>1</v>
       </c>
       <c r="AG120" s="5">
-        <v>3302400.00</v>
+        <v>4761260.00</v>
       </c>
       <c r="AH120" s="5">
-        <v>1381478.40</v>
+        <v>402360.00</v>
       </c>
       <c r="AI120" t="s">
         <v>9</v>
@@ -14855,10 +14915,10 @@
     </row>
     <row r="121" spans="1:38">
       <c r="A121" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="B121" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C121" t="s">
         <v>2</v>
@@ -14867,16 +14927,16 @@
         <v>46199</v>
       </c>
       <c r="E121" t="s">
-        <v>137</v>
+        <v>221</v>
       </c>
       <c r="F121" t="s">
         <v>1</v>
       </c>
       <c r="G121" s="2">
-        <v>45997</v>
+        <v>46197</v>
       </c>
       <c r="H121" s="2">
-        <v>46135</v>
+        <v>46199</v>
       </c>
       <c r="I121" t="s">
         <v>4</v>
@@ -14888,10 +14948,10 @@
         <v>40</v>
       </c>
       <c r="L121" t="s">
-        <v>41</v>
+        <v>131</v>
       </c>
       <c r="M121" t="s">
-        <v>42</v>
+        <v>132</v>
       </c>
       <c r="N121" t="s">
         <v>9</v>
@@ -14903,35 +14963,35 @@
         <v>9</v>
       </c>
       <c r="Q121" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="R121" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="S121" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="T121" t="s">
         <v>13</v>
       </c>
       <c r="U121" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="V121" s="3">
-        <v>30000.000</v>
+        <v>70000.000</v>
       </c>
       <c r="W121" s="3">
         <v>0.000</v>
       </c>
       <c r="X121" s="3">
-        <v>30000.000</v>
+        <v>70000.000</v>
       </c>
       <c r="Y121" t="s">
         <v>15</v>
       </c>
       <c r="Z121" s="2"/>
       <c r="AA121" s="2">
-        <v>46202</v>
+        <v>46211</v>
       </c>
       <c r="AB121" s="2">
         <v>46204</v>
@@ -14940,7 +15000,7 @@
         <v>0</v>
       </c>
       <c r="AD121" s="5">
-        <v>15.36</v>
+        <v>47.90</v>
       </c>
       <c r="AE121" t="s">
         <v>16</v>
@@ -14949,7 +15009,7 @@
         <v>1</v>
       </c>
       <c r="AG121" s="5">
-        <v>460800.00</v>
+        <v>3353000.00</v>
       </c>
       <c r="AH121" s="5">
         <v>0.00</v>
@@ -14969,7 +15029,7 @@
     </row>
     <row r="122" spans="1:38">
       <c r="A122" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="B122" t="s">
         <v>1</v>
@@ -14981,16 +15041,16 @@
         <v>46199</v>
       </c>
       <c r="E122" t="s">
-        <v>188</v>
+        <v>144</v>
       </c>
       <c r="F122" t="s">
         <v>1</v>
       </c>
       <c r="G122" s="2">
-        <v>46164</v>
+        <v>45995</v>
       </c>
       <c r="H122" s="2">
-        <v>46167</v>
+        <v>46135</v>
       </c>
       <c r="I122" t="s">
         <v>4</v>
@@ -15023,7 +15083,7 @@
         <v>44</v>
       </c>
       <c r="S122" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="T122" t="s">
         <v>13</v>
@@ -15032,31 +15092,31 @@
         <v>45</v>
       </c>
       <c r="V122" s="3">
-        <v>217000.000</v>
+        <v>100000.000</v>
       </c>
       <c r="W122" s="3">
-        <v>61960.000</v>
+        <v>100000.000</v>
       </c>
       <c r="X122" s="3">
-        <v>155040.000</v>
+        <v>0.000</v>
       </c>
       <c r="Y122" t="s">
         <v>15</v>
       </c>
       <c r="Z122" s="2">
-        <v>46207</v>
+        <v>46204</v>
       </c>
       <c r="AA122" s="2">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="AB122" s="2">
         <v>46204</v>
       </c>
       <c r="AC122" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD122" s="5">
-        <v>15.29</v>
+        <v>15.31</v>
       </c>
       <c r="AE122" t="s">
         <v>16</v>
@@ -15065,13 +15125,13 @@
         <v>1</v>
       </c>
       <c r="AG122" s="5">
-        <v>3317930.00</v>
+        <v>1531000.00</v>
       </c>
       <c r="AH122" s="5">
-        <v>947368.40</v>
+        <v>1531000.00</v>
       </c>
       <c r="AI122" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AJ122" t="s">
         <v>9</v>
@@ -15085,10 +15145,10 @@
     </row>
     <row r="123" spans="1:38">
       <c r="A123" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="B123" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C123" t="s">
         <v>2</v>
@@ -15097,7 +15157,7 @@
         <v>46199</v>
       </c>
       <c r="E123" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="F123" t="s">
         <v>1</v>
@@ -15118,10 +15178,10 @@
         <v>40</v>
       </c>
       <c r="L123" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="M123" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="N123" t="s">
         <v>9</v>
@@ -15139,7 +15199,7 @@
         <v>44</v>
       </c>
       <c r="S123" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="T123" t="s">
         <v>13</v>
@@ -15148,31 +15208,31 @@
         <v>45</v>
       </c>
       <c r="V123" s="3">
-        <v>60000.000</v>
+        <v>110000.000</v>
       </c>
       <c r="W123" s="3">
-        <v>29980.000</v>
+        <v>110000.000</v>
       </c>
       <c r="X123" s="3">
-        <v>30020.000</v>
+        <v>0.000</v>
       </c>
       <c r="Y123" t="s">
         <v>15</v>
       </c>
       <c r="Z123" s="2">
-        <v>46212</v>
+        <v>46207</v>
       </c>
       <c r="AA123" s="2">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="AB123" s="2">
         <v>46204</v>
       </c>
       <c r="AC123" s="4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AD123" s="5">
-        <v>16.15</v>
+        <v>15.31</v>
       </c>
       <c r="AE123" t="s">
         <v>16</v>
@@ -15181,13 +15241,13 @@
         <v>1</v>
       </c>
       <c r="AG123" s="5">
-        <v>969000.00</v>
+        <v>1684100.00</v>
       </c>
       <c r="AH123" s="5">
-        <v>484177.00</v>
+        <v>1684100.00</v>
       </c>
       <c r="AI123" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AJ123" t="s">
         <v>9</v>
@@ -15201,43 +15261,43 @@
     </row>
     <row r="124" spans="1:38">
       <c r="A124" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="B124" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C124" t="s">
         <v>2</v>
       </c>
       <c r="D124" s="2">
-        <v>46203</v>
+        <v>46199</v>
       </c>
       <c r="E124" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="F124" t="s">
         <v>1</v>
       </c>
       <c r="G124" s="2">
-        <v>46120</v>
+        <v>46164</v>
       </c>
       <c r="H124" s="2">
-        <v>46122</v>
+        <v>46199</v>
       </c>
       <c r="I124" t="s">
         <v>4</v>
       </c>
       <c r="J124" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="K124" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L124" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="M124" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="N124" t="s">
         <v>9</v>
@@ -15249,10 +15309,10 @@
         <v>9</v>
       </c>
       <c r="Q124" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="R124" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="S124" t="s">
         <v>12</v>
@@ -15261,32 +15321,34 @@
         <v>13</v>
       </c>
       <c r="U124" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="V124" s="3">
-        <v>550000.000</v>
+        <v>300000.000</v>
       </c>
       <c r="W124" s="3">
-        <v>0.000</v>
+        <v>209720.000</v>
       </c>
       <c r="X124" s="3">
-        <v>550000.000</v>
+        <v>90280.000</v>
       </c>
       <c r="Y124" t="s">
         <v>15</v>
       </c>
-      <c r="Z124" s="2"/>
+      <c r="Z124" s="2">
+        <v>46211</v>
+      </c>
       <c r="AA124" s="2">
-        <v>46216</v>
+        <v>46204</v>
       </c>
       <c r="AB124" s="2">
         <v>46204</v>
       </c>
       <c r="AC124" s="4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD124" s="5">
-        <v>5.85</v>
+        <v>15.31</v>
       </c>
       <c r="AE124" t="s">
         <v>16</v>
@@ -15295,10 +15357,10 @@
         <v>1</v>
       </c>
       <c r="AG124" s="5">
-        <v>3217500.00</v>
+        <v>4593000.00</v>
       </c>
       <c r="AH124" s="5">
-        <v>0.00</v>
+        <v>3210813.20</v>
       </c>
       <c r="AI124" t="s">
         <v>9</v>
@@ -15315,43 +15377,43 @@
     </row>
     <row r="125" spans="1:38">
       <c r="A125" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="B125" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="C125" t="s">
         <v>2</v>
       </c>
       <c r="D125" s="2">
-        <v>46203</v>
+        <v>46199</v>
       </c>
       <c r="E125" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="F125" t="s">
         <v>1</v>
       </c>
       <c r="G125" s="2">
-        <v>46120</v>
+        <v>46164</v>
       </c>
       <c r="H125" s="2">
-        <v>46122</v>
+        <v>46199</v>
       </c>
       <c r="I125" t="s">
         <v>4</v>
       </c>
       <c r="J125" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="K125" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L125" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="M125" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="N125" t="s">
         <v>9</v>
@@ -15363,10 +15425,10 @@
         <v>9</v>
       </c>
       <c r="Q125" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="R125" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="S125" t="s">
         <v>12</v>
@@ -15375,23 +15437,23 @@
         <v>13</v>
       </c>
       <c r="U125" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="V125" s="3">
-        <v>550000.000</v>
+        <v>300000.000</v>
       </c>
       <c r="W125" s="3">
         <v>0.000</v>
       </c>
       <c r="X125" s="3">
-        <v>550000.000</v>
+        <v>300000.000</v>
       </c>
       <c r="Y125" t="s">
         <v>15</v>
       </c>
       <c r="Z125" s="2"/>
       <c r="AA125" s="2">
-        <v>46216</v>
+        <v>46204</v>
       </c>
       <c r="AB125" s="2">
         <v>46204</v>
@@ -15400,7 +15462,7 @@
         <v>0</v>
       </c>
       <c r="AD125" s="5">
-        <v>5.85</v>
+        <v>15.31</v>
       </c>
       <c r="AE125" t="s">
         <v>16</v>
@@ -15409,7 +15471,7 @@
         <v>1</v>
       </c>
       <c r="AG125" s="5">
-        <v>3217500.00</v>
+        <v>4593000.00</v>
       </c>
       <c r="AH125" s="5">
         <v>0.00</v>
@@ -15429,43 +15491,43 @@
     </row>
     <row r="126" spans="1:38">
       <c r="A126" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="B126" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="C126" t="s">
         <v>2</v>
       </c>
       <c r="D126" s="2">
-        <v>46203</v>
+        <v>46199</v>
       </c>
       <c r="E126" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="F126" t="s">
         <v>1</v>
       </c>
       <c r="G126" s="2">
-        <v>46120</v>
+        <v>46164</v>
       </c>
       <c r="H126" s="2">
-        <v>46122</v>
+        <v>46199</v>
       </c>
       <c r="I126" t="s">
         <v>4</v>
       </c>
       <c r="J126" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="K126" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L126" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="M126" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="N126" t="s">
         <v>9</v>
@@ -15477,10 +15539,10 @@
         <v>9</v>
       </c>
       <c r="Q126" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="R126" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="S126" t="s">
         <v>12</v>
@@ -15489,23 +15551,23 @@
         <v>13</v>
       </c>
       <c r="U126" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="V126" s="3">
-        <v>550000.000</v>
+        <v>90000.000</v>
       </c>
       <c r="W126" s="3">
         <v>0.000</v>
       </c>
       <c r="X126" s="3">
-        <v>550000.000</v>
+        <v>90000.000</v>
       </c>
       <c r="Y126" t="s">
         <v>15</v>
       </c>
       <c r="Z126" s="2"/>
       <c r="AA126" s="2">
-        <v>46216</v>
+        <v>46204</v>
       </c>
       <c r="AB126" s="2">
         <v>46204</v>
@@ -15514,7 +15576,7 @@
         <v>0</v>
       </c>
       <c r="AD126" s="5">
-        <v>5.85</v>
+        <v>15.31</v>
       </c>
       <c r="AE126" t="s">
         <v>16</v>
@@ -15523,7 +15585,7 @@
         <v>1</v>
       </c>
       <c r="AG126" s="5">
-        <v>3217500.00</v>
+        <v>1377900.00</v>
       </c>
       <c r="AH126" s="5">
         <v>0.00</v>
@@ -15543,7 +15605,7 @@
     </row>
     <row r="127" spans="1:38">
       <c r="A127" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="B127" t="s">
         <v>1</v>
@@ -15552,34 +15614,34 @@
         <v>2</v>
       </c>
       <c r="D127" s="2">
-        <v>46203</v>
+        <v>46199</v>
       </c>
       <c r="E127" t="s">
-        <v>195</v>
+        <v>128</v>
       </c>
       <c r="F127" t="s">
         <v>1</v>
       </c>
       <c r="G127" s="2">
+        <v>45890</v>
+      </c>
+      <c r="H127" s="2">
         <v>46120</v>
-      </c>
-      <c r="H127" s="2">
-        <v>46122</v>
       </c>
       <c r="I127" t="s">
         <v>4</v>
       </c>
       <c r="J127" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="K127" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L127" t="s">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="M127" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="N127" t="s">
         <v>9</v>
@@ -15591,46 +15653,44 @@
         <v>9</v>
       </c>
       <c r="Q127" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="R127" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="S127" t="s">
         <v>25</v>
       </c>
       <c r="T127" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="U127" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="V127" s="3">
-        <v>340000.000</v>
+        <v>22500.000</v>
       </c>
       <c r="W127" s="3">
-        <v>19580.000</v>
+        <v>0.000</v>
       </c>
       <c r="X127" s="3">
-        <v>320420.000</v>
+        <v>22500.000</v>
       </c>
       <c r="Y127" t="s">
         <v>15</v>
       </c>
-      <c r="Z127" s="2">
-        <v>46205</v>
-      </c>
+      <c r="Z127" s="2"/>
       <c r="AA127" s="2">
-        <v>46216</v>
+        <v>46203</v>
       </c>
       <c r="AB127" s="2">
         <v>46204</v>
       </c>
       <c r="AC127" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD127" s="5">
-        <v>5.07</v>
+        <v>15.38</v>
       </c>
       <c r="AE127" t="s">
         <v>16</v>
@@ -15639,10 +15699,10 @@
         <v>1</v>
       </c>
       <c r="AG127" s="5">
-        <v>1723800.00</v>
+        <v>346050.00</v>
       </c>
       <c r="AH127" s="5">
-        <v>99270.60</v>
+        <v>0.00</v>
       </c>
       <c r="AI127" t="s">
         <v>9</v>
@@ -15659,43 +15719,43 @@
     </row>
     <row r="128" spans="1:38">
       <c r="A128" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="B128" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C128" t="s">
         <v>2</v>
       </c>
       <c r="D128" s="2">
-        <v>46203</v>
+        <v>46199</v>
       </c>
       <c r="E128" t="s">
-        <v>217</v>
+        <v>148</v>
       </c>
       <c r="F128" t="s">
         <v>1</v>
       </c>
       <c r="G128" s="2">
-        <v>46105</v>
+        <v>45997</v>
       </c>
       <c r="H128" s="2">
-        <v>46105</v>
+        <v>46135</v>
       </c>
       <c r="I128" t="s">
         <v>4</v>
       </c>
       <c r="J128" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="K128" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L128" t="s">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="M128" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="N128" t="s">
         <v>9</v>
@@ -15707,28 +15767,28 @@
         <v>9</v>
       </c>
       <c r="Q128" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="R128" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="S128" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="T128" t="s">
         <v>13</v>
       </c>
       <c r="U128" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="V128" s="3">
-        <v>20000.000</v>
+        <v>40000.000</v>
       </c>
       <c r="W128" s="3">
-        <v>19490.000</v>
+        <v>29980.000</v>
       </c>
       <c r="X128" s="3">
-        <v>0.000</v>
+        <v>10020.000</v>
       </c>
       <c r="Y128" t="s">
         <v>15</v>
@@ -15737,7 +15797,7 @@
         <v>46206</v>
       </c>
       <c r="AA128" s="2">
-        <v>46216</v>
+        <v>46203</v>
       </c>
       <c r="AB128" s="2">
         <v>46204</v>
@@ -15746,7 +15806,7 @@
         <v>2</v>
       </c>
       <c r="AD128" s="5">
-        <v>6.24</v>
+        <v>15.38</v>
       </c>
       <c r="AE128" t="s">
         <v>16</v>
@@ -15755,13 +15815,13 @@
         <v>1</v>
       </c>
       <c r="AG128" s="5">
-        <v>124800.00</v>
+        <v>615200.00</v>
       </c>
       <c r="AH128" s="5">
-        <v>121617.60</v>
+        <v>461092.40</v>
       </c>
       <c r="AI128" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AJ128" t="s">
         <v>9</v>
@@ -15775,43 +15835,43 @@
     </row>
     <row r="129" spans="1:38">
       <c r="A129" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="B129" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C129" t="s">
         <v>2</v>
       </c>
       <c r="D129" s="2">
-        <v>46203</v>
+        <v>46199</v>
       </c>
       <c r="E129" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="F129" t="s">
         <v>1</v>
       </c>
       <c r="G129" s="2">
-        <v>46120</v>
+        <v>46164</v>
       </c>
       <c r="H129" s="2">
-        <v>46122</v>
+        <v>46199</v>
       </c>
       <c r="I129" t="s">
         <v>4</v>
       </c>
       <c r="J129" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="K129" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L129" t="s">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="M129" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="N129" t="s">
         <v>9</v>
@@ -15823,46 +15883,46 @@
         <v>9</v>
       </c>
       <c r="Q129" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="R129" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="S129" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="T129" t="s">
         <v>13</v>
       </c>
       <c r="U129" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="V129" s="3">
-        <v>450000.000</v>
+        <v>240000.000</v>
       </c>
       <c r="W129" s="3">
-        <v>18880.000</v>
+        <v>29980.000</v>
       </c>
       <c r="X129" s="3">
-        <v>431120.000</v>
+        <v>210020.000</v>
       </c>
       <c r="Y129" t="s">
         <v>15</v>
       </c>
       <c r="Z129" s="2">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="AA129" s="2">
-        <v>46216</v>
+        <v>46203</v>
       </c>
       <c r="AB129" s="2">
         <v>46204</v>
       </c>
       <c r="AC129" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD129" s="5">
-        <v>6.24</v>
+        <v>15.38</v>
       </c>
       <c r="AE129" t="s">
         <v>16</v>
@@ -15871,10 +15931,10 @@
         <v>1</v>
       </c>
       <c r="AG129" s="5">
-        <v>2808000.00</v>
+        <v>3691200.00</v>
       </c>
       <c r="AH129" s="5">
-        <v>117811.20</v>
+        <v>461092.40</v>
       </c>
       <c r="AI129" t="s">
         <v>9</v>
@@ -15891,7 +15951,7 @@
     </row>
     <row r="130" spans="1:38">
       <c r="A130" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B130" t="s">
         <v>1</v>
@@ -15900,34 +15960,34 @@
         <v>2</v>
       </c>
       <c r="D130" s="2">
-        <v>46203</v>
+        <v>46199</v>
       </c>
       <c r="E130" t="s">
-        <v>220</v>
+        <v>126</v>
       </c>
       <c r="F130" t="s">
         <v>1</v>
       </c>
       <c r="G130" s="2">
+        <v>45890</v>
+      </c>
+      <c r="H130" s="2">
         <v>46120</v>
-      </c>
-      <c r="H130" s="2">
-        <v>46122</v>
       </c>
       <c r="I130" t="s">
         <v>4</v>
       </c>
       <c r="J130" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="K130" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L130" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="M130" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="N130" t="s">
         <v>9</v>
@@ -15939,44 +15999,46 @@
         <v>9</v>
       </c>
       <c r="Q130" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="R130" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="S130" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="T130" t="s">
         <v>13</v>
       </c>
       <c r="U130" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="V130" s="3">
-        <v>350000.000</v>
+        <v>215000.000</v>
       </c>
       <c r="W130" s="3">
-        <v>0.000</v>
+        <v>89940.000</v>
       </c>
       <c r="X130" s="3">
-        <v>350000.000</v>
+        <v>125060.000</v>
       </c>
       <c r="Y130" t="s">
         <v>15</v>
       </c>
-      <c r="Z130" s="2"/>
+      <c r="Z130" s="2">
+        <v>46207</v>
+      </c>
       <c r="AA130" s="2">
-        <v>46216</v>
+        <v>46202</v>
       </c>
       <c r="AB130" s="2">
         <v>46204</v>
       </c>
       <c r="AC130" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD130" s="5">
-        <v>6.24</v>
+        <v>15.36</v>
       </c>
       <c r="AE130" t="s">
         <v>16</v>
@@ -15985,10 +16047,10 @@
         <v>1</v>
       </c>
       <c r="AG130" s="5">
-        <v>2184000.00</v>
+        <v>3302400.00</v>
       </c>
       <c r="AH130" s="5">
-        <v>0.00</v>
+        <v>1381478.40</v>
       </c>
       <c r="AI130" t="s">
         <v>9</v>
@@ -16005,7 +16067,7 @@
     </row>
     <row r="131" spans="1:38">
       <c r="A131" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B131" t="s">
         <v>19</v>
@@ -16014,34 +16076,34 @@
         <v>2</v>
       </c>
       <c r="D131" s="2">
-        <v>46203</v>
+        <v>46199</v>
       </c>
       <c r="E131" t="s">
-        <v>197</v>
+        <v>146</v>
       </c>
       <c r="F131" t="s">
         <v>1</v>
       </c>
       <c r="G131" s="2">
-        <v>46105</v>
+        <v>45997</v>
       </c>
       <c r="H131" s="2">
-        <v>46105</v>
+        <v>46135</v>
       </c>
       <c r="I131" t="s">
         <v>4</v>
       </c>
       <c r="J131" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="K131" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L131" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="M131" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="N131" t="s">
         <v>9</v>
@@ -16053,35 +16115,35 @@
         <v>9</v>
       </c>
       <c r="Q131" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="R131" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="S131" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="T131" t="s">
         <v>13</v>
       </c>
       <c r="U131" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="V131" s="3">
-        <v>20000.000</v>
+        <v>30000.000</v>
       </c>
       <c r="W131" s="3">
         <v>0.000</v>
       </c>
       <c r="X131" s="3">
-        <v>20000.000</v>
+        <v>30000.000</v>
       </c>
       <c r="Y131" t="s">
         <v>15</v>
       </c>
       <c r="Z131" s="2"/>
       <c r="AA131" s="2">
-        <v>46216</v>
+        <v>46202</v>
       </c>
       <c r="AB131" s="2">
         <v>46204</v>
@@ -16090,7 +16152,7 @@
         <v>0</v>
       </c>
       <c r="AD131" s="5">
-        <v>6.24</v>
+        <v>15.36</v>
       </c>
       <c r="AE131" t="s">
         <v>16</v>
@@ -16099,7 +16161,7 @@
         <v>1</v>
       </c>
       <c r="AG131" s="5">
-        <v>124800.00</v>
+        <v>460800.00</v>
       </c>
       <c r="AH131" s="5">
         <v>0.00</v>
@@ -16119,7 +16181,7 @@
     </row>
     <row r="132" spans="1:38">
       <c r="A132" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B132" t="s">
         <v>1</v>
@@ -16128,34 +16190,34 @@
         <v>2</v>
       </c>
       <c r="D132" s="2">
-        <v>46203</v>
+        <v>46199</v>
       </c>
       <c r="E132" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="F132" t="s">
         <v>1</v>
       </c>
       <c r="G132" s="2">
-        <v>46120</v>
+        <v>46164</v>
       </c>
       <c r="H132" s="2">
-        <v>46122</v>
+        <v>46167</v>
       </c>
       <c r="I132" t="s">
         <v>4</v>
       </c>
       <c r="J132" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="K132" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L132" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="M132" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="N132" t="s">
         <v>9</v>
@@ -16167,44 +16229,46 @@
         <v>9</v>
       </c>
       <c r="Q132" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="R132" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="S132" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="T132" t="s">
         <v>13</v>
       </c>
       <c r="U132" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="V132" s="3">
-        <v>100000.000</v>
+        <v>217000.000</v>
       </c>
       <c r="W132" s="3">
-        <v>0.000</v>
+        <v>61960.000</v>
       </c>
       <c r="X132" s="3">
-        <v>100000.000</v>
+        <v>155040.000</v>
       </c>
       <c r="Y132" t="s">
         <v>15</v>
       </c>
-      <c r="Z132" s="2"/>
+      <c r="Z132" s="2">
+        <v>46207</v>
+      </c>
       <c r="AA132" s="2">
-        <v>46216</v>
+        <v>46202</v>
       </c>
       <c r="AB132" s="2">
         <v>46204</v>
       </c>
       <c r="AC132" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD132" s="5">
-        <v>7.76</v>
+        <v>15.29</v>
       </c>
       <c r="AE132" t="s">
         <v>16</v>
@@ -16213,21 +16277,1169 @@
         <v>1</v>
       </c>
       <c r="AG132" s="5">
+        <v>3317930.00</v>
+      </c>
+      <c r="AH132" s="5">
+        <v>947368.40</v>
+      </c>
+      <c r="AI132" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ132" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK132" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL132" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="133" spans="1:38">
+      <c r="A133" t="s">
+        <v>230</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1</v>
+      </c>
+      <c r="C133" t="s">
+        <v>2</v>
+      </c>
+      <c r="D133" s="2">
+        <v>46199</v>
+      </c>
+      <c r="E133" t="s">
+        <v>186</v>
+      </c>
+      <c r="F133" t="s">
+        <v>1</v>
+      </c>
+      <c r="G133" s="2">
+        <v>46164</v>
+      </c>
+      <c r="H133" s="2">
+        <v>46167</v>
+      </c>
+      <c r="I133" t="s">
+        <v>4</v>
+      </c>
+      <c r="J133" t="s">
+        <v>39</v>
+      </c>
+      <c r="K133" t="s">
+        <v>40</v>
+      </c>
+      <c r="L133" t="s">
+        <v>50</v>
+      </c>
+      <c r="M133" t="s">
+        <v>51</v>
+      </c>
+      <c r="N133" t="s">
+        <v>9</v>
+      </c>
+      <c r="O133" t="s">
+        <v>9</v>
+      </c>
+      <c r="P133" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>43</v>
+      </c>
+      <c r="R133" t="s">
+        <v>44</v>
+      </c>
+      <c r="S133" t="s">
+        <v>34</v>
+      </c>
+      <c r="T133" t="s">
+        <v>13</v>
+      </c>
+      <c r="U133" t="s">
+        <v>45</v>
+      </c>
+      <c r="V133" s="3">
+        <v>60000.000</v>
+      </c>
+      <c r="W133" s="3">
+        <v>29980.000</v>
+      </c>
+      <c r="X133" s="3">
+        <v>30020.000</v>
+      </c>
+      <c r="Y133" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z133" s="2">
+        <v>46212</v>
+      </c>
+      <c r="AA133" s="2">
+        <v>46203</v>
+      </c>
+      <c r="AB133" s="2">
+        <v>46204</v>
+      </c>
+      <c r="AC133" s="4">
+        <v>8</v>
+      </c>
+      <c r="AD133" s="5">
+        <v>16.15</v>
+      </c>
+      <c r="AE133" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF133" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG133" s="5">
+        <v>969000.00</v>
+      </c>
+      <c r="AH133" s="5">
+        <v>484177.00</v>
+      </c>
+      <c r="AI133" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ133" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK133" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL133" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="134" spans="1:38">
+      <c r="A134" t="s">
+        <v>231</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1</v>
+      </c>
+      <c r="C134" t="s">
+        <v>2</v>
+      </c>
+      <c r="D134" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E134" t="s">
+        <v>232</v>
+      </c>
+      <c r="F134" t="s">
+        <v>1</v>
+      </c>
+      <c r="G134" s="2">
+        <v>46120</v>
+      </c>
+      <c r="H134" s="2">
+        <v>46122</v>
+      </c>
+      <c r="I134" t="s">
+        <v>4</v>
+      </c>
+      <c r="J134" t="s">
+        <v>5</v>
+      </c>
+      <c r="K134" t="s">
+        <v>6</v>
+      </c>
+      <c r="L134" t="s">
+        <v>7</v>
+      </c>
+      <c r="M134" t="s">
+        <v>8</v>
+      </c>
+      <c r="N134" t="s">
+        <v>9</v>
+      </c>
+      <c r="O134" t="s">
+        <v>9</v>
+      </c>
+      <c r="P134" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>10</v>
+      </c>
+      <c r="R134" t="s">
+        <v>11</v>
+      </c>
+      <c r="S134" t="s">
+        <v>12</v>
+      </c>
+      <c r="T134" t="s">
+        <v>13</v>
+      </c>
+      <c r="U134" t="s">
+        <v>14</v>
+      </c>
+      <c r="V134" s="3">
+        <v>550000.000</v>
+      </c>
+      <c r="W134" s="3">
+        <v>0.000</v>
+      </c>
+      <c r="X134" s="3">
+        <v>550000.000</v>
+      </c>
+      <c r="Y134" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z134" s="2"/>
+      <c r="AA134" s="2">
+        <v>46216</v>
+      </c>
+      <c r="AB134" s="2">
+        <v>46204</v>
+      </c>
+      <c r="AC134" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD134" s="5">
+        <v>5.85</v>
+      </c>
+      <c r="AE134" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF134" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG134" s="5">
+        <v>3217500.00</v>
+      </c>
+      <c r="AH134" s="5">
+        <v>0.00</v>
+      </c>
+      <c r="AI134" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ134" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK134" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL134" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="135" spans="1:38">
+      <c r="A135" t="s">
+        <v>231</v>
+      </c>
+      <c r="B135" t="s">
+        <v>19</v>
+      </c>
+      <c r="C135" t="s">
+        <v>2</v>
+      </c>
+      <c r="D135" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E135" t="s">
+        <v>233</v>
+      </c>
+      <c r="F135" t="s">
+        <v>1</v>
+      </c>
+      <c r="G135" s="2">
+        <v>46120</v>
+      </c>
+      <c r="H135" s="2">
+        <v>46122</v>
+      </c>
+      <c r="I135" t="s">
+        <v>4</v>
+      </c>
+      <c r="J135" t="s">
+        <v>5</v>
+      </c>
+      <c r="K135" t="s">
+        <v>6</v>
+      </c>
+      <c r="L135" t="s">
+        <v>7</v>
+      </c>
+      <c r="M135" t="s">
+        <v>8</v>
+      </c>
+      <c r="N135" t="s">
+        <v>9</v>
+      </c>
+      <c r="O135" t="s">
+        <v>9</v>
+      </c>
+      <c r="P135" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>10</v>
+      </c>
+      <c r="R135" t="s">
+        <v>11</v>
+      </c>
+      <c r="S135" t="s">
+        <v>12</v>
+      </c>
+      <c r="T135" t="s">
+        <v>13</v>
+      </c>
+      <c r="U135" t="s">
+        <v>14</v>
+      </c>
+      <c r="V135" s="3">
+        <v>550000.000</v>
+      </c>
+      <c r="W135" s="3">
+        <v>0.000</v>
+      </c>
+      <c r="X135" s="3">
+        <v>550000.000</v>
+      </c>
+      <c r="Y135" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z135" s="2"/>
+      <c r="AA135" s="2">
+        <v>46216</v>
+      </c>
+      <c r="AB135" s="2">
+        <v>46204</v>
+      </c>
+      <c r="AC135" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD135" s="5">
+        <v>5.85</v>
+      </c>
+      <c r="AE135" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF135" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG135" s="5">
+        <v>3217500.00</v>
+      </c>
+      <c r="AH135" s="5">
+        <v>0.00</v>
+      </c>
+      <c r="AI135" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ135" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK135" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL135" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="136" spans="1:38">
+      <c r="A136" t="s">
+        <v>231</v>
+      </c>
+      <c r="B136" t="s">
+        <v>21</v>
+      </c>
+      <c r="C136" t="s">
+        <v>2</v>
+      </c>
+      <c r="D136" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E136" t="s">
+        <v>234</v>
+      </c>
+      <c r="F136" t="s">
+        <v>1</v>
+      </c>
+      <c r="G136" s="2">
+        <v>46120</v>
+      </c>
+      <c r="H136" s="2">
+        <v>46122</v>
+      </c>
+      <c r="I136" t="s">
+        <v>4</v>
+      </c>
+      <c r="J136" t="s">
+        <v>5</v>
+      </c>
+      <c r="K136" t="s">
+        <v>6</v>
+      </c>
+      <c r="L136" t="s">
+        <v>7</v>
+      </c>
+      <c r="M136" t="s">
+        <v>8</v>
+      </c>
+      <c r="N136" t="s">
+        <v>9</v>
+      </c>
+      <c r="O136" t="s">
+        <v>9</v>
+      </c>
+      <c r="P136" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>10</v>
+      </c>
+      <c r="R136" t="s">
+        <v>11</v>
+      </c>
+      <c r="S136" t="s">
+        <v>12</v>
+      </c>
+      <c r="T136" t="s">
+        <v>13</v>
+      </c>
+      <c r="U136" t="s">
+        <v>14</v>
+      </c>
+      <c r="V136" s="3">
+        <v>550000.000</v>
+      </c>
+      <c r="W136" s="3">
+        <v>0.000</v>
+      </c>
+      <c r="X136" s="3">
+        <v>550000.000</v>
+      </c>
+      <c r="Y136" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z136" s="2"/>
+      <c r="AA136" s="2">
+        <v>46216</v>
+      </c>
+      <c r="AB136" s="2">
+        <v>46204</v>
+      </c>
+      <c r="AC136" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD136" s="5">
+        <v>5.85</v>
+      </c>
+      <c r="AE136" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF136" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG136" s="5">
+        <v>3217500.00</v>
+      </c>
+      <c r="AH136" s="5">
+        <v>0.00</v>
+      </c>
+      <c r="AI136" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ136" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK136" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL136" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="137" spans="1:38">
+      <c r="A137" t="s">
+        <v>235</v>
+      </c>
+      <c r="B137" t="s">
+        <v>1</v>
+      </c>
+      <c r="C137" t="s">
+        <v>2</v>
+      </c>
+      <c r="D137" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E137" t="s">
+        <v>204</v>
+      </c>
+      <c r="F137" t="s">
+        <v>1</v>
+      </c>
+      <c r="G137" s="2">
+        <v>46120</v>
+      </c>
+      <c r="H137" s="2">
+        <v>46122</v>
+      </c>
+      <c r="I137" t="s">
+        <v>4</v>
+      </c>
+      <c r="J137" t="s">
+        <v>5</v>
+      </c>
+      <c r="K137" t="s">
+        <v>6</v>
+      </c>
+      <c r="L137" t="s">
+        <v>7</v>
+      </c>
+      <c r="M137" t="s">
+        <v>8</v>
+      </c>
+      <c r="N137" t="s">
+        <v>9</v>
+      </c>
+      <c r="O137" t="s">
+        <v>9</v>
+      </c>
+      <c r="P137" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>10</v>
+      </c>
+      <c r="R137" t="s">
+        <v>11</v>
+      </c>
+      <c r="S137" t="s">
+        <v>25</v>
+      </c>
+      <c r="T137" t="s">
+        <v>9</v>
+      </c>
+      <c r="U137" t="s">
+        <v>14</v>
+      </c>
+      <c r="V137" s="3">
+        <v>340000.000</v>
+      </c>
+      <c r="W137" s="3">
+        <v>19580.000</v>
+      </c>
+      <c r="X137" s="3">
+        <v>320420.000</v>
+      </c>
+      <c r="Y137" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z137" s="2">
+        <v>46205</v>
+      </c>
+      <c r="AA137" s="2">
+        <v>46216</v>
+      </c>
+      <c r="AB137" s="2">
+        <v>46204</v>
+      </c>
+      <c r="AC137" s="4">
+        <v>1</v>
+      </c>
+      <c r="AD137" s="5">
+        <v>5.07</v>
+      </c>
+      <c r="AE137" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF137" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG137" s="5">
+        <v>1723800.00</v>
+      </c>
+      <c r="AH137" s="5">
+        <v>99270.60</v>
+      </c>
+      <c r="AI137" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ137" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK137" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL137" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="138" spans="1:38">
+      <c r="A138" t="s">
+        <v>236</v>
+      </c>
+      <c r="B138" t="s">
+        <v>1</v>
+      </c>
+      <c r="C138" t="s">
+        <v>2</v>
+      </c>
+      <c r="D138" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E138" t="s">
+        <v>237</v>
+      </c>
+      <c r="F138" t="s">
+        <v>1</v>
+      </c>
+      <c r="G138" s="2">
+        <v>46105</v>
+      </c>
+      <c r="H138" s="2">
+        <v>46105</v>
+      </c>
+      <c r="I138" t="s">
+        <v>4</v>
+      </c>
+      <c r="J138" t="s">
+        <v>5</v>
+      </c>
+      <c r="K138" t="s">
+        <v>6</v>
+      </c>
+      <c r="L138" t="s">
+        <v>7</v>
+      </c>
+      <c r="M138" t="s">
+        <v>8</v>
+      </c>
+      <c r="N138" t="s">
+        <v>9</v>
+      </c>
+      <c r="O138" t="s">
+        <v>9</v>
+      </c>
+      <c r="P138" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>10</v>
+      </c>
+      <c r="R138" t="s">
+        <v>11</v>
+      </c>
+      <c r="S138" t="s">
+        <v>28</v>
+      </c>
+      <c r="T138" t="s">
+        <v>13</v>
+      </c>
+      <c r="U138" t="s">
+        <v>14</v>
+      </c>
+      <c r="V138" s="3">
+        <v>20000.000</v>
+      </c>
+      <c r="W138" s="3">
+        <v>19490.000</v>
+      </c>
+      <c r="X138" s="3">
+        <v>0.000</v>
+      </c>
+      <c r="Y138" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z138" s="2">
+        <v>46206</v>
+      </c>
+      <c r="AA138" s="2">
+        <v>46216</v>
+      </c>
+      <c r="AB138" s="2">
+        <v>46204</v>
+      </c>
+      <c r="AC138" s="4">
+        <v>2</v>
+      </c>
+      <c r="AD138" s="5">
+        <v>6.24</v>
+      </c>
+      <c r="AE138" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF138" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG138" s="5">
+        <v>124800.00</v>
+      </c>
+      <c r="AH138" s="5">
+        <v>121617.60</v>
+      </c>
+      <c r="AI138" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ138" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK138" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL138" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="139" spans="1:38">
+      <c r="A139" t="s">
+        <v>236</v>
+      </c>
+      <c r="B139" t="s">
+        <v>19</v>
+      </c>
+      <c r="C139" t="s">
+        <v>2</v>
+      </c>
+      <c r="D139" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E139" t="s">
+        <v>238</v>
+      </c>
+      <c r="F139" t="s">
+        <v>1</v>
+      </c>
+      <c r="G139" s="2">
+        <v>46120</v>
+      </c>
+      <c r="H139" s="2">
+        <v>46122</v>
+      </c>
+      <c r="I139" t="s">
+        <v>4</v>
+      </c>
+      <c r="J139" t="s">
+        <v>5</v>
+      </c>
+      <c r="K139" t="s">
+        <v>6</v>
+      </c>
+      <c r="L139" t="s">
+        <v>7</v>
+      </c>
+      <c r="M139" t="s">
+        <v>8</v>
+      </c>
+      <c r="N139" t="s">
+        <v>9</v>
+      </c>
+      <c r="O139" t="s">
+        <v>9</v>
+      </c>
+      <c r="P139" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>10</v>
+      </c>
+      <c r="R139" t="s">
+        <v>11</v>
+      </c>
+      <c r="S139" t="s">
+        <v>28</v>
+      </c>
+      <c r="T139" t="s">
+        <v>13</v>
+      </c>
+      <c r="U139" t="s">
+        <v>14</v>
+      </c>
+      <c r="V139" s="3">
+        <v>450000.000</v>
+      </c>
+      <c r="W139" s="3">
+        <v>18880.000</v>
+      </c>
+      <c r="X139" s="3">
+        <v>431120.000</v>
+      </c>
+      <c r="Y139" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z139" s="2">
+        <v>46211</v>
+      </c>
+      <c r="AA139" s="2">
+        <v>46216</v>
+      </c>
+      <c r="AB139" s="2">
+        <v>46204</v>
+      </c>
+      <c r="AC139" s="4">
+        <v>7</v>
+      </c>
+      <c r="AD139" s="5">
+        <v>6.24</v>
+      </c>
+      <c r="AE139" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF139" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG139" s="5">
+        <v>2808000.00</v>
+      </c>
+      <c r="AH139" s="5">
+        <v>117811.20</v>
+      </c>
+      <c r="AI139" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ139" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK139" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL139" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="140" spans="1:38">
+      <c r="A140" t="s">
+        <v>239</v>
+      </c>
+      <c r="B140" t="s">
+        <v>1</v>
+      </c>
+      <c r="C140" t="s">
+        <v>2</v>
+      </c>
+      <c r="D140" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E140" t="s">
+        <v>240</v>
+      </c>
+      <c r="F140" t="s">
+        <v>1</v>
+      </c>
+      <c r="G140" s="2">
+        <v>46120</v>
+      </c>
+      <c r="H140" s="2">
+        <v>46122</v>
+      </c>
+      <c r="I140" t="s">
+        <v>4</v>
+      </c>
+      <c r="J140" t="s">
+        <v>5</v>
+      </c>
+      <c r="K140" t="s">
+        <v>6</v>
+      </c>
+      <c r="L140" t="s">
+        <v>7</v>
+      </c>
+      <c r="M140" t="s">
+        <v>8</v>
+      </c>
+      <c r="N140" t="s">
+        <v>9</v>
+      </c>
+      <c r="O140" t="s">
+        <v>9</v>
+      </c>
+      <c r="P140" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>10</v>
+      </c>
+      <c r="R140" t="s">
+        <v>11</v>
+      </c>
+      <c r="S140" t="s">
+        <v>31</v>
+      </c>
+      <c r="T140" t="s">
+        <v>13</v>
+      </c>
+      <c r="U140" t="s">
+        <v>14</v>
+      </c>
+      <c r="V140" s="3">
+        <v>350000.000</v>
+      </c>
+      <c r="W140" s="3">
+        <v>0.000</v>
+      </c>
+      <c r="X140" s="3">
+        <v>350000.000</v>
+      </c>
+      <c r="Y140" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z140" s="2"/>
+      <c r="AA140" s="2">
+        <v>46216</v>
+      </c>
+      <c r="AB140" s="2">
+        <v>46204</v>
+      </c>
+      <c r="AC140" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD140" s="5">
+        <v>6.24</v>
+      </c>
+      <c r="AE140" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF140" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG140" s="5">
+        <v>2184000.00</v>
+      </c>
+      <c r="AH140" s="5">
+        <v>0.00</v>
+      </c>
+      <c r="AI140" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ140" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK140" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL140" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="141" spans="1:38">
+      <c r="A141" t="s">
+        <v>239</v>
+      </c>
+      <c r="B141" t="s">
+        <v>19</v>
+      </c>
+      <c r="C141" t="s">
+        <v>2</v>
+      </c>
+      <c r="D141" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E141" t="s">
+        <v>206</v>
+      </c>
+      <c r="F141" t="s">
+        <v>1</v>
+      </c>
+      <c r="G141" s="2">
+        <v>46105</v>
+      </c>
+      <c r="H141" s="2">
+        <v>46105</v>
+      </c>
+      <c r="I141" t="s">
+        <v>4</v>
+      </c>
+      <c r="J141" t="s">
+        <v>5</v>
+      </c>
+      <c r="K141" t="s">
+        <v>6</v>
+      </c>
+      <c r="L141" t="s">
+        <v>7</v>
+      </c>
+      <c r="M141" t="s">
+        <v>8</v>
+      </c>
+      <c r="N141" t="s">
+        <v>9</v>
+      </c>
+      <c r="O141" t="s">
+        <v>9</v>
+      </c>
+      <c r="P141" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>10</v>
+      </c>
+      <c r="R141" t="s">
+        <v>11</v>
+      </c>
+      <c r="S141" t="s">
+        <v>31</v>
+      </c>
+      <c r="T141" t="s">
+        <v>13</v>
+      </c>
+      <c r="U141" t="s">
+        <v>14</v>
+      </c>
+      <c r="V141" s="3">
+        <v>20000.000</v>
+      </c>
+      <c r="W141" s="3">
+        <v>0.000</v>
+      </c>
+      <c r="X141" s="3">
+        <v>20000.000</v>
+      </c>
+      <c r="Y141" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z141" s="2"/>
+      <c r="AA141" s="2">
+        <v>46216</v>
+      </c>
+      <c r="AB141" s="2">
+        <v>46204</v>
+      </c>
+      <c r="AC141" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD141" s="5">
+        <v>6.24</v>
+      </c>
+      <c r="AE141" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF141" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG141" s="5">
+        <v>124800.00</v>
+      </c>
+      <c r="AH141" s="5">
+        <v>0.00</v>
+      </c>
+      <c r="AI141" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ141" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK141" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL141" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="142" spans="1:38">
+      <c r="A142" t="s">
+        <v>241</v>
+      </c>
+      <c r="B142" t="s">
+        <v>1</v>
+      </c>
+      <c r="C142" t="s">
+        <v>2</v>
+      </c>
+      <c r="D142" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E142" t="s">
+        <v>242</v>
+      </c>
+      <c r="F142" t="s">
+        <v>1</v>
+      </c>
+      <c r="G142" s="2">
+        <v>46120</v>
+      </c>
+      <c r="H142" s="2">
+        <v>46122</v>
+      </c>
+      <c r="I142" t="s">
+        <v>4</v>
+      </c>
+      <c r="J142" t="s">
+        <v>5</v>
+      </c>
+      <c r="K142" t="s">
+        <v>6</v>
+      </c>
+      <c r="L142" t="s">
+        <v>7</v>
+      </c>
+      <c r="M142" t="s">
+        <v>8</v>
+      </c>
+      <c r="N142" t="s">
+        <v>9</v>
+      </c>
+      <c r="O142" t="s">
+        <v>9</v>
+      </c>
+      <c r="P142" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>10</v>
+      </c>
+      <c r="R142" t="s">
+        <v>11</v>
+      </c>
+      <c r="S142" t="s">
+        <v>34</v>
+      </c>
+      <c r="T142" t="s">
+        <v>13</v>
+      </c>
+      <c r="U142" t="s">
+        <v>14</v>
+      </c>
+      <c r="V142" s="3">
+        <v>100000.000</v>
+      </c>
+      <c r="W142" s="3">
+        <v>0.000</v>
+      </c>
+      <c r="X142" s="3">
+        <v>100000.000</v>
+      </c>
+      <c r="Y142" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z142" s="2"/>
+      <c r="AA142" s="2">
+        <v>46216</v>
+      </c>
+      <c r="AB142" s="2">
+        <v>46204</v>
+      </c>
+      <c r="AC142" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD142" s="5">
+        <v>7.76</v>
+      </c>
+      <c r="AE142" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF142" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG142" s="5">
         <v>776000.00</v>
       </c>
-      <c r="AH132" s="5">
+      <c r="AH142" s="5">
         <v>0.00</v>
       </c>
-      <c r="AI132" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ132" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK132" t="s">
-        <v>9</v>
-      </c>
-      <c r="AL132" t="s">
+      <c r="AI142" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ142" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK142" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL142" t="s">
         <v>18</v>
       </c>
     </row>

--- a/PO_matcall.XLSX
+++ b/PO_matcall.XLSX
@@ -166,7 +166,7 @@
     <t>0010027535</t>
   </si>
   <si>
-    <t>แปซิฟิก ชูการ์ คอร์ปอเรชั่น</t>
+    <t>Pacific Sugar Corporation Limited</t>
   </si>
   <si>
     <t>0105090136</t>
@@ -487,7 +487,7 @@
     <t>0010006985</t>
   </si>
   <si>
-    <t>ดับเบิ้ลยูจีซี</t>
+    <t>WGC CO.,LTD.</t>
   </si>
   <si>
     <t>0105104205</t>
@@ -9313,10 +9313,10 @@
         <v>195000.000</v>
       </c>
       <c r="W72" s="3">
-        <v>99950.000</v>
+        <v>129990.000</v>
       </c>
       <c r="X72" s="3">
-        <v>95050.000</v>
+        <v>65010.000</v>
       </c>
       <c r="Y72" t="s">
         <v>15</v>
@@ -9346,7 +9346,7 @@
         <v>2827500.00</v>
       </c>
       <c r="AH72" s="5">
-        <v>1449275.00</v>
+        <v>1884855.00</v>
       </c>
       <c r="AI72" t="s">
         <v>9</v>
@@ -10119,10 +10119,10 @@
         <v>260000.000</v>
       </c>
       <c r="W79" s="3">
-        <v>229970.000</v>
+        <v>260000.000</v>
       </c>
       <c r="X79" s="3">
-        <v>30030.000</v>
+        <v>0.000</v>
       </c>
       <c r="Y79" t="s">
         <v>15</v>
@@ -10152,10 +10152,10 @@
         <v>3770000.00</v>
       </c>
       <c r="AH79" s="5">
-        <v>3334565.00</v>
+        <v>3770000.00</v>
       </c>
       <c r="AI79" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AJ79" t="s">
         <v>9</v>
@@ -10929,10 +10929,10 @@
         <v>60000.000</v>
       </c>
       <c r="W86" s="3">
-        <v>50000.000</v>
+        <v>60000.000</v>
       </c>
       <c r="X86" s="3">
-        <v>10000.000</v>
+        <v>0.000</v>
       </c>
       <c r="Y86" t="s">
         <v>15</v>
@@ -10962,10 +10962,10 @@
         <v>945000.00</v>
       </c>
       <c r="AH86" s="5">
-        <v>787500.00</v>
+        <v>945000.00</v>
       </c>
       <c r="AI86" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AJ86" t="s">
         <v>9</v>
@@ -11045,15 +11045,17 @@
         <v>140000.000</v>
       </c>
       <c r="W87" s="3">
-        <v>0.000</v>
+        <v>15010.000</v>
       </c>
       <c r="X87" s="3">
-        <v>140000.000</v>
+        <v>124990.000</v>
       </c>
       <c r="Y87" t="s">
         <v>15</v>
       </c>
-      <c r="Z87" s="2"/>
+      <c r="Z87" s="2">
+        <v>46218</v>
+      </c>
       <c r="AA87" s="2">
         <v>46146</v>
       </c>
@@ -11061,7 +11063,7 @@
         <v>46143</v>
       </c>
       <c r="AC87" s="4">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AD87" s="5">
         <v>15.75</v>
@@ -11076,7 +11078,7 @@
         <v>2205000.00</v>
       </c>
       <c r="AH87" s="5">
-        <v>0.00</v>
+        <v>236407.50</v>
       </c>
       <c r="AI87" t="s">
         <v>9</v>
@@ -11739,10 +11741,10 @@
         <v>530000.000</v>
       </c>
       <c r="W93" s="3">
-        <v>360340.000</v>
+        <v>341640.000</v>
       </c>
       <c r="X93" s="3">
-        <v>0.000</v>
+        <v>188360.000</v>
       </c>
       <c r="Y93" t="s">
         <v>15</v>
@@ -11772,10 +11774,10 @@
         <v>3015700.00</v>
       </c>
       <c r="AH93" s="5">
-        <v>2050334.60</v>
+        <v>1943931.60</v>
       </c>
       <c r="AI93" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AJ93" t="s">
         <v>9</v>
@@ -15327,10 +15329,10 @@
         <v>300000.000</v>
       </c>
       <c r="W124" s="3">
-        <v>209720.000</v>
+        <v>239700.000</v>
       </c>
       <c r="X124" s="3">
-        <v>90280.000</v>
+        <v>60300.000</v>
       </c>
       <c r="Y124" t="s">
         <v>15</v>
@@ -15360,7 +15362,7 @@
         <v>4593000.00</v>
       </c>
       <c r="AH124" s="5">
-        <v>3210813.20</v>
+        <v>3669807.00</v>
       </c>
       <c r="AI124" t="s">
         <v>9</v>
@@ -15671,15 +15673,17 @@
         <v>22500.000</v>
       </c>
       <c r="W127" s="3">
+        <v>22500.000</v>
+      </c>
+      <c r="X127" s="3">
         <v>0.000</v>
-      </c>
-      <c r="X127" s="3">
-        <v>22500.000</v>
       </c>
       <c r="Y127" t="s">
         <v>15</v>
       </c>
-      <c r="Z127" s="2"/>
+      <c r="Z127" s="2">
+        <v>46219</v>
+      </c>
       <c r="AA127" s="2">
         <v>46203</v>
       </c>
@@ -15687,7 +15691,7 @@
         <v>46204</v>
       </c>
       <c r="AC127" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AD127" s="5">
         <v>15.38</v>
@@ -15702,10 +15706,10 @@
         <v>346050.00</v>
       </c>
       <c r="AH127" s="5">
-        <v>0.00</v>
+        <v>346050.00</v>
       </c>
       <c r="AI127" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AJ127" t="s">
         <v>9</v>
@@ -15785,10 +15789,10 @@
         <v>40000.000</v>
       </c>
       <c r="W128" s="3">
-        <v>29980.000</v>
+        <v>37460.000</v>
       </c>
       <c r="X128" s="3">
-        <v>10020.000</v>
+        <v>2540.000</v>
       </c>
       <c r="Y128" t="s">
         <v>15</v>
@@ -15818,7 +15822,7 @@
         <v>615200.00</v>
       </c>
       <c r="AH128" s="5">
-        <v>461092.40</v>
+        <v>576134.80</v>
       </c>
       <c r="AI128" t="s">
         <v>9</v>
@@ -16479,15 +16483,17 @@
         <v>550000.000</v>
       </c>
       <c r="W134" s="3">
-        <v>0.000</v>
+        <v>76590.000</v>
       </c>
       <c r="X134" s="3">
-        <v>550000.000</v>
+        <v>473410.000</v>
       </c>
       <c r="Y134" t="s">
         <v>15</v>
       </c>
-      <c r="Z134" s="2"/>
+      <c r="Z134" s="2">
+        <v>46205</v>
+      </c>
       <c r="AA134" s="2">
         <v>46216</v>
       </c>
@@ -16495,7 +16501,7 @@
         <v>46204</v>
       </c>
       <c r="AC134" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD134" s="5">
         <v>5.85</v>
@@ -16510,7 +16516,7 @@
         <v>3217500.00</v>
       </c>
       <c r="AH134" s="5">
-        <v>0.00</v>
+        <v>448051.50</v>
       </c>
       <c r="AI134" t="s">
         <v>9</v>
@@ -16593,15 +16599,17 @@
         <v>550000.000</v>
       </c>
       <c r="W135" s="3">
-        <v>0.000</v>
+        <v>76130.000</v>
       </c>
       <c r="X135" s="3">
-        <v>550000.000</v>
+        <v>473870.000</v>
       </c>
       <c r="Y135" t="s">
         <v>15</v>
       </c>
-      <c r="Z135" s="2"/>
+      <c r="Z135" s="2">
+        <v>46210</v>
+      </c>
       <c r="AA135" s="2">
         <v>46216</v>
       </c>
@@ -16609,7 +16617,7 @@
         <v>46204</v>
       </c>
       <c r="AC135" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD135" s="5">
         <v>5.85</v>
@@ -16624,7 +16632,7 @@
         <v>3217500.00</v>
       </c>
       <c r="AH135" s="5">
-        <v>0.00</v>
+        <v>445360.50</v>
       </c>
       <c r="AI135" t="s">
         <v>9</v>
